--- a/Data/IP_SeperationofPower.xlsx
+++ b/Data/IP_SeperationofPower.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -472,1056 +472,1056 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>What is the doctrine of Separation of Powers?</t>
+          <t>In the Indian Constitution, is the separation of powers absolute?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Division of government powers among Legislature, Executive, Judiciary</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Sharing powers among political parties</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Concentration of power in one organ</t>
+          <t>Partially</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Division of powers between Centre and State</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Division of government powers among Legislature, Executive, Judiciary</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>It means each branch has distinct functions.</t>
+          <t>India follows partial separation with checks and balances.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Who is known as the Father of the Doctrine of Separation of Powers?</t>
+          <t>Executive power flows from</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>John Locke</t>
+          <t>Legislature</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Montesquieu</t>
+          <t>Judiciary</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Thomas Hobbes</t>
+          <t>President</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jean-Jacques Rousseau</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Montesquieu</t>
+          <t>President</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>He popularized the concept in “The Spirit of Laws”.</t>
+          <t>The President is the nominal executive head.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3</v>
+        <v>47</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>In the Indian Constitution, is the separation of powers absolute?</t>
+          <t>The Legislature can</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Make laws</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Interpret laws</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Partially</t>
+          <t>Enforce laws</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Make laws</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>India follows partial separation with checks and balances.</t>
+          <t>Its primary function is lawmaking.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4</v>
+        <v>58</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Which branch makes laws according to the doctrine of separation of powers?</t>
+          <t>Judicial independence in India is protected by</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Executive</t>
+          <t>Security of tenure</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Judiciary</t>
+          <t>Fixed salary</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Legislature</t>
+          <t>Prohibition of arbitrary removal</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Police</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Legislature</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Legislature enacts laws.</t>
+          <t>Ensures impartiality and fairness.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>5</v>
+        <v>68</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Which branch implements the laws?</t>
+          <t>Which is the primary function of the Judiciary?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Legislature</t>
+          <t>Make laws</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Executive</t>
+          <t>Enforce laws</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Judiciary</t>
+          <t>Interpret laws</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Press</t>
+          <t>Administer laws</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Executive</t>
+          <t>Interpret laws</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Responsible for enforcing laws.</t>
+          <t>Judiciary interprets laws and Constitution.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Which branch interprets the laws?</t>
+          <t>Who is known as the Father of the Doctrine of Separation of Powers?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Legislature</t>
+          <t>John Locke</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Executive</t>
+          <t>Montesquieu</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Judiciary</t>
+          <t>Thomas Hobbes</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Police</t>
+          <t>Jean-Jacques Rousseau</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Judiciary</t>
+          <t>Montesquieu</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Courts interpret laws.</t>
+          <t>He popularized the concept in “The Spirit of Laws”.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>7</v>
+        <v>75</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Which article of the Indian Constitution mentions separation of powers explicitly?</t>
+          <t>The Constitution of India was adopted in which year?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Article 50</t>
+          <t>1947</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Article 368</t>
+          <t>1949</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Article 14</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>No article</t>
+          <t>1952</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>No article</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>It is implied, not explicitly mentioned.</t>
+          <t>Adopted on 26 January 1950.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>The principle of Separation of Powers helps to</t>
+          <t>The power to impeach the President lies with</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Prevent misuse of power</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Concentrate power</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Make laws faster</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Increase political parties</t>
+          <t>Constitutional Court</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Prevent misuse of power</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Avoids arbitrary rule.</t>
+          <t>Parliament initiates impeachment.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>9</v>
+        <v>87</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>The Executive in India is responsible to</t>
+          <t>The executive in India is</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>The President</t>
+          <t>Constitutional and political</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>The Judiciary</t>
+          <t>Absolute</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>The Parliament</t>
+          <t>Legislative</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>The Police</t>
+          <t>Judicial</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>The Parliament</t>
+          <t>Constitutional and political</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>It is responsible to the legislature.</t>
+          <t>It functions within constitutional limits.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Which body checks the actions of the Executive?</t>
+          <t>The Indian Constitution provides for</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Judiciary</t>
+          <t>Absolute separation of powers</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Legislature</t>
+          <t>Partial separation with checks</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Press</t>
+          <t>No separation of powers</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Military</t>
+          <t>Fusion of powers</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Judiciary</t>
+          <t>Partial separation with checks</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Judicial review controls Executive excess.</t>
+          <t>Balances power among organs.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>11</v>
+        <v>80</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Judicial review is an example of</t>
+          <t>The doctrine of separation of powers was introduced to</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Judiciary checking Legislature</t>
+          <t>Avoid concentration of power</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Executive controlling Judiciary</t>
+          <t>Ensure efficiency</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Legislature controlling Executive</t>
+          <t>Promote unity</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Legislature checking Judiciary</t>
+          <t>Centralize authority</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Judiciary checking Legislature</t>
+          <t>Avoid concentration of power</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Ensures laws are constitutional.</t>
+          <t>Prevents abuse of power.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Who appoints the Chief Justice of India?</t>
+          <t>Separation of powers helps in</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Consolidating power</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Democracy and accountability</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Dictatorship</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Supreme Court Judges</t>
+          <t>Political stability only</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Democracy and accountability</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>The President appoints CJI.</t>
+          <t>Ensures balanced governance.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Which is a feature of partial separation of powers in India?</t>
+          <t>Separation of powers ensures</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Judges can be executive officers</t>
+          <t>Concentration of power</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Legislature controls Judiciary</t>
+          <t>Checks and balances</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Executive is responsible to Legislature</t>
+          <t>Conflicts among organs</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>No checks and balances</t>
+          <t>Political deadlock</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Executive is responsible to Legislature</t>
+          <t>Checks and balances</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Shows overlap but with accountability.</t>
+          <t>Prevents abuse of power.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>14</v>
+        <v>99</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Which famous case discussed separation of powers and judicial independence?</t>
+          <t>Which organ appoints the Prime Minister?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Kesavananda Bharati</t>
+          <t>President</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Minerva Mills</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Golaknath</t>
+          <t>Chief Justice</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Minerva Mills</t>
+          <t>President</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Emphasized balance between powers.</t>
+          <t>President appoints PM who commands majority.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>15</v>
+        <v>84</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Who suggested the idea of separation of powers in Indian Constitution drafting?</t>
+          <t>Which Article in Indian Constitution provides for the separation of judiciary from executive?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>B.R. Ambedkar</t>
+          <t>Article 50</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Mahatma Gandhi</t>
+          <t>Article 51</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Jawaharlal Nehru</t>
+          <t>Article 44</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>All of them</t>
+          <t>Article 52</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>B.R. Ambedkar</t>
+          <t>Article 50</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>He explained doctrine in the Constituent Assembly.</t>
+          <t>Directive Principle for judicial independence.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>16</v>
+        <v>93</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>The Legislature can</t>
+          <t>Who is called the ‘Guardian of the Constitution’?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Make laws</t>
+          <t>President</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Enforce laws</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Interpret laws</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>None of the above</t>
+          <t>Attorney General</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Make laws</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Its primary function is lawmaking.</t>
+          <t>Protects constitutional rights.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>The Executive</t>
+          <t>Legislative power in India</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Can veto laws</t>
+          <t>Is exercised by Parliament</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Enforces laws</t>
+          <t>Is exercised by President alone</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Interprets laws</t>
+          <t>Is exercised by Judiciary</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Both a and c</t>
+          <t>Is exercised by Executive alone</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Enforces laws</t>
+          <t>Is exercised by Parliament</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Executes and administers laws.</t>
+          <t>Parliament legislates laws.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>18</v>
+        <v>89</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>The Judiciary</t>
+          <t>The independence of judiciary in India is protected by</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Declares laws unconstitutional</t>
+          <t>Security of tenure and fixed salaries</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Enforces laws</t>
+          <t>Appointment by Legislature</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Makes laws</t>
+          <t>Removal by Executive</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Both a and c</t>
+          <t>Approval by Parliament</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Declares laws unconstitutional</t>
+          <t>Security of tenure and fixed salaries</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Protects constitutionality.</t>
+          <t>Ensures impartial judiciary.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>19</v>
+        <v>63</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Is there any overlap between powers in Indian system?</t>
+          <t>Which organ approves the budget?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Legislature</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Only in emergencies</t>
+          <t>Judiciary</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Finance Commission</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Legislature</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Overlap exists but balanced by checks.</t>
+          <t>Parliament approves government budget.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Who said “Power tends to corrupt, and absolute power corrupts absolutely”?</t>
+          <t>The judiciary in India is independent because</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Montesquieu</t>
+          <t>Judges have security of tenure</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Lord Acton</t>
+          <t>Judges are appointed by Parliament</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>John Locke</t>
+          <t>Judges can be removed easily</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>James Madison</t>
+          <t>Judges report to Executive</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lord Acton</t>
+          <t>Judges have security of tenure</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Warned about concentration of power.</t>
+          <t>Ensures impartial decisions.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>The separation of powers in India is</t>
+          <t>Who said “Power tends to corrupt, and absolute power corrupts absolutely”?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Strict</t>
+          <t>Montesquieu</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Flexible</t>
+          <t>Lord Acton</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Absent</t>
+          <t>John Locke</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Unconstitutional</t>
+          <t>James Madison</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Flexible</t>
+          <t>Lord Acton</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Allows cooperation among branches.</t>
+          <t>Warned about concentration of power.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Legislative power in India</t>
+          <t>The power to issue ordinances lies with</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Is exercised by Parliament</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Is exercised by President alone</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Is exercised by Judiciary</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Is exercised by Executive alone</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Is exercised by Parliament</t>
+          <t>President</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Parliament legislates laws.</t>
+          <t>President can promulgate ordinances.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>23</v>
+        <v>67</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Executive power flows from</t>
+          <t>Which organ has the power to amend the Constitution?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Legislature</t>
+          <t>Judiciary</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Judiciary</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
+          <t>Parliament</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
           <t>President</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Supreme Court</t>
-        </is>
-      </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>The President is the nominal executive head.</t>
+          <t>Legislature can amend Constitution under Article 368.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Judiciary independence is protected by</t>
+          <t>The term ‘checks and balances’ means</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Fixed tenure of judges</t>
+          <t>Each organ checks the other’s powers</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Security of tenure</t>
+          <t>All powers are in one organ</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Independence of appointment</t>
+          <t>Judiciary controls all</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Executive controls Legislature</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Each organ checks the other’s powers</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Ensures impartial judiciary.</t>
+          <t>Prevents power abuse.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Separation of powers helps in</t>
+          <t>The system where powers overlap but are balanced is called</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Consolidating power</t>
+          <t>Fusion of Powers</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Democracy and accountability</t>
+          <t>Separation of Powers</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Dictatorship</t>
+          <t>Partial Fusion</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Political stability only</t>
+          <t>Checks and Balances</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Democracy and accountability</t>
+          <t>Checks and Balances</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Ensures balanced governance.</t>
+          <t>Ensures mutual accountability.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>26</v>
+        <v>85</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Which of the following is NOT a basic feature of the Indian Constitution?</t>
+          <t>The power of the Judiciary to review the Constitutionality of a law is called</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Separation of Powers</t>
+          <t>Judicial review</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Federalism</t>
+          <t>Judicial activism</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Judicial Review</t>
+          <t>Judicial restraint</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Absolute Separation of Powers</t>
+          <t>Judicial supremacy</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Absolute Separation of Powers</t>
+          <t>Judicial review</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>India follows partial separation, not absolute.</t>
+          <t>A key feature of Indian judiciary.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>27</v>
+        <v>62</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Which organ has the power to make laws in India?</t>
+          <t>In India, the Supreme Court acts as a</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Judiciary</t>
+          <t>Legislature</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Legislature</t>
+          <t>Guardian of the Constitution</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1541,587 +1541,587 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Legislature</t>
+          <t>Guardian of the Constitution</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Legislature makes laws.</t>
+          <t>It protects constitutional rights.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>28</v>
+        <v>66</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Which organ enforces the laws in India?</t>
+          <t>The power to promulgate ordinances rests with</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Judiciary</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Executive</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Legislature</t>
+          <t>Speaker of Lok Sabha</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>None of the above</t>
+          <t>Chief Justice</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Executive</t>
+          <t>President</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>The executive implements laws.</t>
+          <t>Under Article 123, President can issue ordinances.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>The Indian Constitution follows which kind of separation of powers?</t>
+          <t>Which principle limits the powers of government organs?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Strict Separation</t>
+          <t>Judicial Activism</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Partial Separation</t>
+          <t>Separation of Powers</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>No Separation</t>
+          <t>Federalism</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Complete Merger</t>
+          <t>Universal Adult Franchise</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Partial Separation</t>
+          <t>Separation of Powers</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Separation with checks and balances.</t>
+          <t>Divides power among branches.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Which organ of government appoints judges in India?</t>
+          <t>The President of India is part of which organ?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Legislature</t>
+          <t>Executive only</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Executive</t>
+          <t>Legislature only</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Judiciary itself</t>
+          <t>Both Executive and Legislature</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>President on recommendation</t>
+          <t>Judiciary</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>President on recommendation</t>
+          <t>Both Executive and Legislature</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>President appoints judges on recommendations.</t>
+          <t>President is head of Executive and Parliament.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>31</v>
+        <v>73</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Which Article of the Indian Constitution provides for the appointment of the Chief Justice of India?</t>
+          <t>Which organ is responsible for framing the policies of the government?</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Article 124</t>
+          <t>Legislature</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Article 217</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Article 50</t>
+          <t>Judiciary</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Article 368</t>
+          <t>Press</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Article 124</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Provides appointment procedure.</t>
+          <t>Executes and formulates policies.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>32</v>
+        <v>78</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>The doctrine of separation of powers was first developed by?</t>
+          <t>Which of the following is a check by the Legislature on the Executive?</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Montesquieu</t>
+          <t>Judicial Review</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>John Locke</t>
+          <t>Vote of No-Confidence</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Thomas Hobbes</t>
+          <t>Ordinance Power</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Jean-Jacques Rousseau</t>
+          <t>Appointment of Judges</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Montesquieu</t>
+          <t>Vote of No-Confidence</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>He introduced the concept.</t>
+          <t>Legislature can remove the government by this motion.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Judicial review in India is exercised by</t>
+          <t>In Indian Constitution, which organ has the power to dissolve the Lok Sabha?</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Supreme Court only</t>
+          <t>President</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>High Courts only</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Both Supreme Court and High Courts</t>
+          <t>Chief Justice</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Both Supreme Court and High Courts</t>
+          <t>President</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Both levels have power of judicial review.</t>
+          <t>On advice of Prime Minister.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Which of the following cases emphasized the importance of separation of powers?</t>
+          <t>Who ensures that the Executive functions according to the law?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Kesavananda Bharati</t>
+          <t>Judiciary</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Minerva Mills</t>
+          <t>Legislature</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Golak Nath</t>
+          <t>President</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Indira Gandhi Case</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Kesavananda Bharati</t>
+          <t>Judiciary</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Upheld basic structure doctrine including separation of powers.</t>
+          <t>Through judicial review and writ jurisdiction.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>The power of the Executive to reject laws passed by Legislature is called</t>
+          <t>Who is the head of the Legislature in India?</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Judicial Review</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Veto Power</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ordinance Power</t>
+          <t>Speaker of Lok Sabha</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Amendment Power</t>
+          <t>Chief Justice</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Veto Power</t>
+          <t>President</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>President can veto bills.</t>
+          <t>He is the head of Parliament.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Who holds the real executive power in India?</t>
+          <t>What is the doctrine of Separation of Powers?</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Division of government powers among Legislature, Executive, Judiciary</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Prime Minister and Council of Ministers</t>
+          <t>Sharing powers among political parties</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Concentration of power in one organ</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Division of powers between Centre and State</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Prime Minister and Council of Ministers</t>
+          <t>Division of government powers among Legislature, Executive, Judiciary</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>They hold actual power.</t>
+          <t>It means each branch has distinct functions.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Separation of powers ensures</t>
+          <t>Which organ of the government is known as the ‘sword arm’ of the state?</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Concentration of power</t>
+          <t>Legislature</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Checks and balances</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Conflicts among organs</t>
+          <t>Judiciary</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Political deadlock</t>
+          <t>Press</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Checks and balances</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Prevents abuse of power.</t>
+          <t>The Executive enforces laws and maintains order.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Which organ interprets the Constitution?</t>
+          <t>Which of the following is NOT a function of the Executive?</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Legislature</t>
+          <t>Implementing laws</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Executive</t>
+          <t>Making laws</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Judiciary</t>
+          <t>Administering policies</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Maintaining public order</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Judiciary</t>
+          <t>Making laws</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Courts interpret laws and Constitution.</t>
+          <t>Lawmaking is primarily Legislature's function.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>The judiciary in India is independent because</t>
+          <t>The Executive</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Judges have security of tenure</t>
+          <t>Can veto laws</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Judges are appointed by Parliament</t>
+          <t>Enforces laws</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Judges can be removed easily</t>
+          <t>Interprets laws</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Judges report to Executive</t>
+          <t>Both a and c</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Judges have security of tenure</t>
+          <t>Enforces laws</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Ensures impartial decisions.</t>
+          <t>Executes and administers laws.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Which principle limits the powers of government organs?</t>
+          <t>Which branch implements the laws?</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Judicial Activism</t>
+          <t>Legislature</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Separation of Powers</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Federalism</t>
+          <t>Judiciary</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Universal Adult Franchise</t>
+          <t>Press</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Separation of Powers</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Divides power among branches.</t>
+          <t>Responsible for enforcing laws.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>41</v>
+        <v>12</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>The President of India is part of which organ?</t>
+          <t>Who appoints the Chief Justice of India?</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Executive only</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Legislature only</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Both Executive and Legislature</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Judiciary</t>
+          <t>Supreme Court Judges</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Both Executive and Legislature</t>
+          <t>President</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>President is head of Executive and Parliament.</t>
+          <t>The President appoints CJI.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>42</v>
+        <v>77</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>The power to issue ordinances lies with</t>
+          <t>Who holds the power to dissolve the Lok Sabha?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Speaker of Lok Sabha</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Chief Justice of India</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2146,377 +2146,377 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>President can promulgate ordinances.</t>
+          <t>Dissolution is done by the President on PM's advice.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>43</v>
+        <v>91</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>The power to impeach the President lies with</t>
+          <t>Which organ controls the government expenditure?</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Legislature</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Executive</t>
+          <t>Judiciary</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Constitutional Court</t>
+          <t>Finance Commission</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Legislature</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Parliament initiates impeachment.</t>
+          <t>Parliament controls budget.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>In India, which organ controls the budget?</t>
+          <t>Which article of the Indian Constitution mentions separation of powers explicitly?</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Executive</t>
+          <t>Article 50</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Legislature</t>
+          <t>Article 368</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Judiciary</t>
+          <t>Article 14</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Press</t>
+          <t>No article</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Legislature</t>
+          <t>No article</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Parliament controls financial powers.</t>
+          <t>It is implied, not explicitly mentioned.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>The system where powers overlap but are balanced is called</t>
+          <t>The Judiciary</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Fusion of Powers</t>
+          <t>Declares laws unconstitutional</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Separation of Powers</t>
+          <t>Enforces laws</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Partial Fusion</t>
+          <t>Makes laws</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Checks and Balances</t>
+          <t>Both a and c</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Checks and Balances</t>
+          <t>Declares laws unconstitutional</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Ensures mutual accountability.</t>
+          <t>Protects constitutionality.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>The Indian Constitution provides for</t>
+          <t>Which case established the power of judicial review in India?</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Absolute separation of powers</t>
+          <t>Kesavananda Bharati</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Partial separation with checks</t>
+          <t>Golaknath</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>No separation of powers</t>
+          <t>Marbury v Madison</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Fusion of powers</t>
+          <t>Minerva Mills</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Partial separation with checks</t>
+          <t>Kesavananda Bharati</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Balances power among organs.</t>
+          <t>It upheld the basic structure doctrine.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>The Legislature can</t>
+          <t>The power of the Executive to reject laws passed by Legislature is called</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Make laws</t>
+          <t>Judicial Review</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Interpret laws</t>
+          <t>Veto Power</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Enforce laws</t>
+          <t>Ordinance Power</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Amendment Power</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Make laws</t>
+          <t>Veto Power</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Its primary function is lawmaking.</t>
+          <t>President can veto bills.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Which organ is responsible for enforcing laws?</t>
+          <t>The President’s power to summon and prorogue Parliament is part of</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Legislature</t>
+          <t>Executive powers</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Executive</t>
+          <t>Legislative powers</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Judiciary</t>
+          <t>Judicial powers</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Both Legislature and Judiciary</t>
+          <t>Financial powers</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Executive</t>
+          <t>Legislative powers</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Executes laws.</t>
+          <t>President as part of Parliament exercises these powers.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>The term ‘checks and balances’ means</t>
+          <t>Judiciary independence is protected by</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Each organ checks the other’s powers</t>
+          <t>Fixed tenure of judges</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>All powers are in one organ</t>
+          <t>Security of tenure</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Judiciary controls all</t>
+          <t>Independence of appointment</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Executive controls Legislature</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Each organ checks the other’s powers</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Prevents power abuse.</t>
+          <t>Ensures impartial judiciary.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>The judiciary can</t>
+          <t>Which of the following best describes the Indian model of separation of powers?</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Strike down unconstitutional laws</t>
+          <t>Absolute and rigid separation</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Pass budgets</t>
+          <t>Flexible and overlapping powers</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Execute laws</t>
+          <t>Complete fusion</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Make treaties</t>
+          <t>No separation</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Strike down unconstitutional laws</t>
+          <t>Flexible and overlapping powers</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>It safeguards Constitution.</t>
+          <t>Allows cooperation with checks.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Which organ of the government is known as the ‘sword arm’ of the state?</t>
+          <t>Which constitutional article mandates the separation of judiciary from executive in India?</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Legislature</t>
+          <t>Article 50</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Executive</t>
+          <t>Article 44</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Judiciary</t>
+          <t>Article 37</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Press</t>
+          <t>Article 51</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Executive</t>
+          <t>Article 50</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>The Executive enforces laws and maintains order.</t>
+          <t>Part of DPSP, directs separation for judicial independence.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Who ensures that the Executive functions according to the law?</t>
+          <t>Which organ enforces the laws in India?</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2526,277 +2526,277 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
+          <t>Executive</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
           <t>Legislature</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>President</t>
-        </is>
-      </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>None of the above</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Judiciary</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Through judicial review and writ jurisdiction.</t>
+          <t>The executive implements laws.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>The power of the Legislature to check the Executive is exercised through</t>
+          <t>The judiciary can</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>No-confidence motion</t>
+          <t>Strike down unconstitutional laws</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Judicial review</t>
+          <t>Pass budgets</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Ordinance power</t>
+          <t>Execute laws</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Amendment power</t>
+          <t>Make treaties</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>No-confidence motion</t>
+          <t>Strike down unconstitutional laws</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>It can remove the government by vote of no-confidence.</t>
+          <t>It safeguards Constitution.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Which constitutional article mandates the separation of judiciary from executive in India?</t>
+          <t>Which body can impeach a Supreme Court judge?</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Article 50</t>
+          <t>President</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Article 44</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Article 37</t>
+          <t>Chief Justice</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Article 51</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Article 50</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Part of DPSP, directs separation for judicial independence.</t>
+          <t>Parliament initiates impeachment proceedings.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>55</v>
+        <v>10</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>The principle of separation of powers helps in</t>
+          <t>Which body checks the actions of the Executive?</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Avoiding dictatorship</t>
+          <t>Judiciary</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Encouraging dictatorship</t>
+          <t>Legislature</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Centralizing power</t>
+          <t>Press</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Undermining democracy</t>
+          <t>Military</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Avoiding dictatorship</t>
+          <t>Judiciary</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Prevents concentration of power.</t>
+          <t>Judicial review controls Executive excess.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>56</v>
+        <v>6</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>The President’s power to summon and prorogue Parliament is part of</t>
+          <t>Which branch interprets the laws?</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Executive powers</t>
+          <t>Legislature</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Legislative powers</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Judicial powers</t>
+          <t>Judiciary</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Financial powers</t>
+          <t>Police</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Legislative powers</t>
+          <t>Judiciary</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>President as part of Parliament exercises these powers.</t>
+          <t>Courts interpret laws.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>57</v>
+        <v>29</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Which of the following is NOT a function of the Executive?</t>
+          <t>The Indian Constitution follows which kind of separation of powers?</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Implementing laws</t>
+          <t>Strict Separation</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Making laws</t>
+          <t>Partial Separation</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Administering policies</t>
+          <t>No Separation</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Maintaining public order</t>
+          <t>Complete Merger</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Making laws</t>
+          <t>Partial Separation</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Lawmaking is primarily Legislature's function.</t>
+          <t>Separation with checks and balances.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Judicial independence in India is protected by</t>
+          <t>The Cabinet is part of which organ?</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Security of tenure</t>
+          <t>Legislature</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Fixed salary</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Prohibition of arbitrary removal</t>
+          <t>Judiciary</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>None of the above</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Ensures impartiality and fairness.</t>
+          <t>It is the real decision-making body of Executive.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>The Cabinet is part of which organ?</t>
+          <t>Which organ is responsible for enforcing laws?</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2816,7 +2816,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>None of the above</t>
+          <t>Both Legislature and Judiciary</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -2826,167 +2826,167 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>It is the real decision-making body of Executive.</t>
+          <t>Executes laws.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>60</v>
+        <v>11</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Who is the head of the Legislature in India?</t>
+          <t>Judicial review is an example of</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Judiciary checking Legislature</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Executive controlling Judiciary</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Speaker of Lok Sabha</t>
+          <t>Legislature controlling Executive</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Chief Justice</t>
+          <t>Legislature checking Judiciary</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Judiciary checking Legislature</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>He is the head of Parliament.</t>
+          <t>Ensures laws are constitutional.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Which body can impeach a Supreme Court judge?</t>
+          <t>In India, which organ controls the budget?</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Legislature</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Chief Justice</t>
+          <t>Judiciary</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Press</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Legislature</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Parliament initiates impeachment proceedings.</t>
+          <t>Parliament controls financial powers.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>62</v>
+        <v>4</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>In India, the Supreme Court acts as a</t>
+          <t>Which branch makes laws according to the doctrine of separation of powers?</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
+          <t>Executive</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Judiciary</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
           <t>Legislature</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>Executive</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>Guardian of the Constitution</t>
-        </is>
-      </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Police</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Guardian of the Constitution</t>
+          <t>Legislature</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>It protects constitutional rights.</t>
+          <t>Legislature enacts laws.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Which organ approves the budget?</t>
+          <t>Who is the constitutional head of the Executive in India?</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Executive</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Legislature</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Judiciary</t>
+          <t>Chief Justice</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Finance Commission</t>
+          <t>Governor</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Legislature</t>
+          <t>President</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Parliament approves government budget.</t>
+          <t>Nominal head of the Executive.</t>
         </is>
       </c>
     </row>
@@ -3032,1371 +3032,1363 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>65</v>
+        <v>86</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Which case established the power of judicial review in India?</t>
+          <t>Who said “Power corrupts; absolute power corrupts absolutely”?</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Kesavananda Bharati</t>
+          <t>Montesquieu</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Golaknath</t>
+          <t>John Locke</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Marbury v Madison</t>
+          <t>Lord Acton</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Minerva Mills</t>
+          <t>Jean-Jacques Rousseau</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Kesavananda Bharati</t>
+          <t>Lord Acton</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>It upheld the basic structure doctrine.</t>
+          <t>A famous quote on power abuse.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>The power to promulgate ordinances rests with</t>
+          <t>Which case declared that the basic structure of the Constitution cannot be altered by Parliament?</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Kesavananda Bharati</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Golaknath</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Speaker of Lok Sabha</t>
+          <t>Minerva Mills</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Chief Justice</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Kesavananda Bharati</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Under Article 123, President can issue ordinances.</t>
+          <t>The landmark basic structure doctrine case.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>67</v>
+        <v>92</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Which organ has the power to amend the Constitution?</t>
+          <t>The power to promulgate ordinances is vested in</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Judiciary</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Executive</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
+          <t>Supreme Court</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
           <t>President</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>Parliament</t>
-        </is>
-      </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Legislature can amend Constitution under Article 368.</t>
+          <t>Under Article 123.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>68</v>
+        <v>33</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Which is the primary function of the Judiciary?</t>
+          <t>Judicial review in India is exercised by</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Make laws</t>
+          <t>Supreme Court only</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Enforce laws</t>
+          <t>High Courts only</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Interpret laws</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>Administer laws</t>
-        </is>
-      </c>
+          <t>Both Supreme Court and High Courts</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Interpret laws</t>
+          <t>Both Supreme Court and High Courts</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Judiciary interprets laws and Constitution.</t>
+          <t>Both levels have power of judicial review.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>In Indian Constitution, which organ has the power to dissolve the Lok Sabha?</t>
+          <t>Which principle states that no one should exercise the powers of more than one branch?</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Checks and balances</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Separation of Powers</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Chief Justice</t>
+          <t>Federalism</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Rule of Law</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Separation of Powers</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>On advice of Prime Minister.</t>
+          <t>Ensures distinct roles.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Which of the following best describes the Indian model of separation of powers?</t>
+          <t>Which article defines the powers of the Supreme Court?</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Absolute and rigid separation</t>
+          <t>Article 124</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Flexible and overlapping powers</t>
+          <t>Article 217</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Complete fusion</t>
+          <t>Article 50</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>No separation</t>
+          <t>Article 368</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Flexible and overlapping powers</t>
+          <t>Article 124</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Allows cooperation with checks.</t>
+          <t>Details appointment and jurisdiction.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>71</v>
+        <v>98</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Judges of the Supreme Court can be removed by</t>
+          <t>The President of India acts on the advice of</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Parliamentary impeachment</t>
+          <t>Prime Minister and Council of Ministers</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Presidential order</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Executive decision</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Judicial verdict</t>
+          <t>Speaker of Lok Sabha</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Parliamentary impeachment</t>
+          <t>Prime Minister and Council of Ministers</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Requires special majority in Parliament.</t>
+          <t>The real executive authority lies with them.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>72</v>
+        <v>9</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Which principle states that no one should exercise the powers of more than one branch?</t>
+          <t>The Executive in India is responsible to</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Checks and balances</t>
+          <t>The President</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Separation of Powers</t>
+          <t>The Judiciary</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Federalism</t>
+          <t>The Parliament</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rule of Law</t>
+          <t>The Police</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Separation of Powers</t>
+          <t>The Parliament</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Ensures distinct roles.</t>
+          <t>It is responsible to the legislature.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Which organ is responsible for framing the policies of the government?</t>
+          <t>The power of the Legislature to check the Executive is exercised through</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Legislature</t>
+          <t>No-confidence motion</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Executive</t>
+          <t>Judicial review</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Judiciary</t>
+          <t>Ordinance power</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Press</t>
+          <t>Amendment power</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Executive</t>
+          <t>No-confidence motion</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Executes and formulates policies.</t>
+          <t>It can remove the government by vote of no-confidence.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>74</v>
+        <v>30</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Who is the constitutional head of the Executive in India?</t>
+          <t>Which organ of government appoints judges in India?</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Legislature</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Chief Justice</t>
+          <t>Judiciary itself</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Governor</t>
+          <t>President on recommendation</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>President on recommendation</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Nominal head of the Executive.</t>
+          <t>President appoints judges on recommendations.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>75</v>
+        <v>26</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>The Constitution of India was adopted in which year?</t>
+          <t>Which of the following is NOT a basic feature of the Indian Constitution?</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>1947</t>
+          <t>Separation of Powers</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>1949</t>
+          <t>Federalism</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>Judicial Review</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>1952</t>
+          <t>Absolute Separation of Powers</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>Absolute Separation of Powers</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Adopted on 26 January 1950.</t>
+          <t>India follows partial separation, not absolute.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Which organ of government in India has the power to grant pardon and reprieve?</t>
+          <t>Judicial review means</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Legislature</t>
+          <t>Making laws</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Executive</t>
+          <t>Interpreting laws and declaring laws unconstitutional</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Judiciary</t>
+          <t>Enforcing laws</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Approving budget</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Executive</t>
+          <t>Interpreting laws and declaring laws unconstitutional</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>The President exercises this power as part of the executive.</t>
+          <t>Ensures laws comply with Constitution.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>77</v>
+        <v>8</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Who holds the power to dissolve the Lok Sabha?</t>
+          <t>The principle of Separation of Powers helps to</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Prevent misuse of power</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Concentrate power</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Speaker of Lok Sabha</t>
+          <t>Make laws faster</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Chief Justice of India</t>
+          <t>Increase political parties</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Prevent misuse of power</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Dissolution is done by the President on PM's advice.</t>
+          <t>Avoids arbitrary rule.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Which of the following is a check by the Legislature on the Executive?</t>
+          <t>Which organ of the government is responsible for implementing laws?</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Judicial Review</t>
+          <t>Legislature</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Vote of No-Confidence</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Ordinance Power</t>
+          <t>Judiciary</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Appointment of Judges</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Vote of No-Confidence</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Legislature can remove the government by this motion.</t>
+          <t>The executive enforces the laws.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Which body is responsible for appointing the judges of the High Courts?</t>
+          <t>The President of India is part of which organs?</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Executive only</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Legislature only</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Chief Justice of India and Governor</t>
+          <t>Both Executive and Legislature</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Judiciary</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Chief Justice of India and Governor</t>
+          <t>Both Executive and Legislature</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Appointment is made by President after consultation.</t>
+          <t>President is constitutional head of both.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>80</v>
+        <v>38</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>The doctrine of separation of powers was introduced to</t>
+          <t>Which organ interprets the Constitution?</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Avoid concentration of power</t>
+          <t>Legislature</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Ensure efficiency</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Promote unity</t>
+          <t>Judiciary</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Centralize authority</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Avoid concentration of power</t>
+          <t>Judiciary</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Prevents abuse of power.</t>
+          <t>Courts interpret laws and Constitution.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Which organ of the government is responsible for implementing laws?</t>
+          <t>The principle of Separation of Powers aims at</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Legislature</t>
+          <t>Centralization of power</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Executive</t>
+          <t>Distribution of powers</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Judiciary</t>
+          <t>Concentration of power</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Merger of powers</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Executive</t>
+          <t>Distribution of powers</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>The executive enforces the laws.</t>
+          <t>Avoids power concentration.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>82</v>
+        <v>13</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Judicial review means</t>
+          <t>Which is a feature of partial separation of powers in India?</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Making laws</t>
+          <t>Judges can be executive officers</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Interpreting laws and declaring laws unconstitutional</t>
+          <t>Legislature controls Judiciary</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Enforcing laws</t>
+          <t>Executive is responsible to Legislature</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Approving budget</t>
+          <t>No checks and balances</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Interpreting laws and declaring laws unconstitutional</t>
+          <t>Executive is responsible to Legislature</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Ensures laws comply with Constitution.</t>
+          <t>Shows overlap but with accountability.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>83</v>
+        <v>15</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>The President of India is part of which organs?</t>
+          <t>Who suggested the idea of separation of powers in Indian Constitution drafting?</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Executive only</t>
+          <t>B.R. Ambedkar</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Legislature only</t>
+          <t>Mahatma Gandhi</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Both Executive and Legislature</t>
+          <t>Jawaharlal Nehru</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Judiciary</t>
+          <t>All of them</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Both Executive and Legislature</t>
+          <t>B.R. Ambedkar</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>President is constitutional head of both.</t>
+          <t>He explained doctrine in the Constituent Assembly.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Which Article in Indian Constitution provides for the separation of judiciary from executive?</t>
+          <t>In India, the power to amend the Constitution lies with</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Article 50</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Article 51</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Article 44</t>
+          <t>Judiciary</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Article 52</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Article 50</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Directive Principle for judicial independence.</t>
+          <t>Under Article 368.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>85</v>
+        <v>36</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>The power of the Judiciary to review the Constitutionality of a law is called</t>
+          <t>Who holds the real executive power in India?</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Judicial review</t>
+          <t>President</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Judicial activism</t>
+          <t>Prime Minister and Council of Ministers</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Judicial restraint</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Judicial supremacy</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Judicial review</t>
+          <t>Prime Minister and Council of Ministers</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>A key feature of Indian judiciary.</t>
+          <t>They hold actual power.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>86</v>
+        <v>34</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Who said “Power corrupts; absolute power corrupts absolutely”?</t>
+          <t>Which of the following cases emphasized the importance of separation of powers?</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Montesquieu</t>
+          <t>Kesavananda Bharati</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>John Locke</t>
+          <t>Minerva Mills</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Lord Acton</t>
+          <t>Golak Nath</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Jean-Jacques Rousseau</t>
+          <t>Indira Gandhi Case</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lord Acton</t>
+          <t>Kesavananda Bharati</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>A famous quote on power abuse.</t>
+          <t>Upheld basic structure doctrine including separation of powers.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>87</v>
+        <v>27</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>The executive in India is</t>
+          <t>Which organ has the power to make laws in India?</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Constitutional and political</t>
+          <t>Judiciary</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Absolute</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Legislative</t>
+          <t>Legislature</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Judicial</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Constitutional and political</t>
+          <t>Legislature</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>It functions within constitutional limits.</t>
+          <t>Legislature makes laws.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Which of the following is a function of the Legislature?</t>
+          <t>The executive is responsible to</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Make laws</t>
+          <t>Legislature</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Implement laws</t>
+          <t>Judiciary</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Interpret laws</t>
+          <t>President</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Enforce laws</t>
+          <t>Election Commission</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Make laws</t>
+          <t>Legislature</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Lawmaking is the primary role.</t>
+          <t>Executive is accountable to Parliament.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>89</v>
+        <v>31</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>The independence of judiciary in India is protected by</t>
+          <t>Which Article of the Indian Constitution provides for the appointment of the Chief Justice of India?</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Security of tenure and fixed salaries</t>
+          <t>Article 124</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Appointment by Legislature</t>
+          <t>Article 217</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Removal by Executive</t>
+          <t>Article 50</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Approval by Parliament</t>
+          <t>Article 368</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Security of tenure and fixed salaries</t>
+          <t>Article 124</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Ensures impartial judiciary.</t>
+          <t>Provides appointment procedure.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Which case declared that the basic structure of the Constitution cannot be altered by Parliament?</t>
+          <t>The separation of powers in India is</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Kesavananda Bharati</t>
+          <t>Strict</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Golaknath</t>
+          <t>Flexible</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Minerva Mills</t>
+          <t>Absent</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Unconstitutional</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Kesavananda Bharati</t>
+          <t>Flexible</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>The landmark basic structure doctrine case.</t>
+          <t>Allows cooperation among branches.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>91</v>
+        <v>19</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Which organ controls the government expenditure?</t>
+          <t>Is there any overlap between powers in Indian system?</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Executive</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Legislature</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Judiciary</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>Finance Commission</t>
-        </is>
-      </c>
+          <t>Only in emergencies</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Legislature</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Parliament controls budget.</t>
+          <t>Overlap exists but balanced by checks.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>92</v>
+        <v>55</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>The power to promulgate ordinances is vested in</t>
+          <t>The principle of separation of powers helps in</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Avoiding dictatorship</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Encouraging dictatorship</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Centralizing power</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Undermining democracy</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Avoiding dictatorship</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Under Article 123.</t>
+          <t>Prevents concentration of power.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>93</v>
+        <v>14</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Who is called the ‘Guardian of the Constitution’?</t>
+          <t>Which famous case discussed separation of powers and judicial independence?</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Kesavananda Bharati</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Minerva Mills</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Attorney General</t>
+          <t>Golaknath</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Minerva Mills</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Protects constitutional rights.</t>
+          <t>Emphasized balance between powers.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>94</v>
+        <v>16</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>In India, the power to amend the Constitution lies with</t>
+          <t>The Legislature can</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Make laws</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Enforce laws</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Judiciary</t>
+          <t>Interpret laws</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>None of the above</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Make laws</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Under Article 368.</t>
+          <t>Its primary function is lawmaking.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>95</v>
+        <v>71</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>The executive is responsible to</t>
+          <t>Judges of the Supreme Court can be removed by</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Legislature</t>
+          <t>Parliamentary impeachment</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Judiciary</t>
+          <t>Presidential order</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Executive decision</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Election Commission</t>
+          <t>Judicial verdict</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Legislature</t>
+          <t>Parliamentary impeachment</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Executive is accountable to Parliament.</t>
+          <t>Requires special majority in Parliament.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>96</v>
+        <v>32</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Which organ enforces law and order?</t>
+          <t>The doctrine of separation of powers was first developed by?</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Judiciary</t>
+          <t>Montesquieu</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Legislature</t>
+          <t>John Locke</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Executive</t>
+          <t>Thomas Hobbes</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Press</t>
+          <t>Jean-Jacques Rousseau</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Executive</t>
+          <t>Montesquieu</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Police and administrative agencies.</t>
+          <t>He introduced the concept.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>The principle of Separation of Powers aims at</t>
+          <t>Which organ enforces law and order?</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Centralization of power</t>
+          <t>Judiciary</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Distribution of powers</t>
+          <t>Legislature</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Concentration of power</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Merger of powers</t>
+          <t>Press</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Distribution of powers</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Avoids power concentration.</t>
+          <t>Police and administrative agencies.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>The President of India acts on the advice of</t>
+          <t>Which of the following is a function of the Legislature?</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Prime Minister and Council of Ministers</t>
+          <t>Make laws</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Implement laws</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Interpret laws</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Speaker of Lok Sabha</t>
+          <t>Enforce laws</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Prime Minister and Council of Ministers</t>
+          <t>Make laws</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>The real executive authority lies with them.</t>
+          <t>Lawmaking is the primary role.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Which organ appoints the Prime Minister?</t>
+          <t>Which body is responsible for appointing the judges of the High Courts?</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -4406,67 +4398,67 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
+          <t>Prime Minister</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Chief Justice of India and Governor</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
           <t>Parliament</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>Supreme Court</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>Chief Justice</t>
-        </is>
-      </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Chief Justice of India and Governor</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>President appoints PM who commands majority.</t>
+          <t>Appointment is made by President after consultation.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>100</v>
+        <v>76</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Which article defines the powers of the Supreme Court?</t>
+          <t>Which organ of government in India has the power to grant pardon and reprieve?</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Article 124</t>
+          <t>Legislature</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Article 217</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Article 50</t>
+          <t>Judiciary</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Article 368</t>
+          <t>President</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Article 124</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Details appointment and jurisdiction.</t>
+          <t>The President exercises this power as part of the executive.</t>
         </is>
       </c>
     </row>

--- a/Data/IP_SeperationofPower.xlsx
+++ b/Data/IP_SeperationofPower.xlsx
@@ -472,1211 +472,1211 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>46</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>In the Indian Constitution, is the separation of powers absolute?</t>
+          <t>The Indian Constitution provides for</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Absolute separation of powers</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Partial separation with checks</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Partially</t>
+          <t>No separation of powers</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Fusion of powers</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Partial separation with checks</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>India follows partial separation with checks and balances.</t>
+          <t>Balances power among organs.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>23</v>
+        <v>87</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Executive power flows from</t>
+          <t>The executive in India is</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Legislature</t>
+          <t>Constitutional and political</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Judiciary</t>
+          <t>Absolute</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Legislative</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Judicial</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Constitutional and political</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>The President is the nominal executive head.</t>
+          <t>It functions within constitutional limits.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>The Legislature can</t>
+          <t>The power to impeach the President lies with</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Make laws</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Interpret laws</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Enforce laws</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Constitutional Court</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Make laws</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Its primary function is lawmaking.</t>
+          <t>Parliament initiates impeachment.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Judicial independence in India is protected by</t>
+          <t>The Constitution of India was adopted in which year?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Security of tenure</t>
+          <t>1947</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Fixed salary</t>
+          <t>1949</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Prohibition of arbitrary removal</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>1952</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Ensures impartiality and fairness.</t>
+          <t>Adopted on 26 January 1950.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>68</v>
+        <v>2</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Which is the primary function of the Judiciary?</t>
+          <t>Who is known as the Father of the Doctrine of Separation of Powers?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Make laws</t>
+          <t>John Locke</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Enforce laws</t>
+          <t>Montesquieu</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Interpret laws</t>
+          <t>Thomas Hobbes</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Administer laws</t>
+          <t>Jean-Jacques Rousseau</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Interpret laws</t>
+          <t>Montesquieu</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Judiciary interprets laws and Constitution.</t>
+          <t>He popularized the concept in “The Spirit of Laws”.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2</v>
+        <v>68</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Who is known as the Father of the Doctrine of Separation of Powers?</t>
+          <t>Which is the primary function of the Judiciary?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>John Locke</t>
+          <t>Make laws</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Montesquieu</t>
+          <t>Enforce laws</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Thomas Hobbes</t>
+          <t>Interpret laws</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Jean-Jacques Rousseau</t>
+          <t>Administer laws</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Montesquieu</t>
+          <t>Interpret laws</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>He popularized the concept in “The Spirit of Laws”.</t>
+          <t>Judiciary interprets laws and Constitution.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>The Constitution of India was adopted in which year?</t>
+          <t>Judicial independence in India is protected by</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1947</t>
+          <t>Security of tenure</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1949</t>
+          <t>Fixed salary</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>Prohibition of arbitrary removal</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1952</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Adopted on 26 January 1950.</t>
+          <t>Ensures impartiality and fairness.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>The power to impeach the President lies with</t>
+          <t>The Legislature can</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Make laws</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Interpret laws</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Executive</t>
+          <t>Enforce laws</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Constitutional Court</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Make laws</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Parliament initiates impeachment.</t>
+          <t>Its primary function is lawmaking.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>87</v>
+        <v>23</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>The executive in India is</t>
+          <t>Executive power flows from</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Constitutional and political</t>
+          <t>Legislature</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Absolute</t>
+          <t>Judiciary</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Legislative</t>
+          <t>President</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Judicial</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Constitutional and political</t>
+          <t>President</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>It functions within constitutional limits.</t>
+          <t>The President is the nominal executive head.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>46</v>
+        <v>3</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>The Indian Constitution provides for</t>
+          <t>In the Indian Constitution, is the separation of powers absolute?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Absolute separation of powers</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Partial separation with checks</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>No separation of powers</t>
+          <t>Partially</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fusion of powers</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Partial separation with checks</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Balances power among organs.</t>
+          <t>India follows partial separation with checks and balances.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>80</v>
+        <v>39</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>The doctrine of separation of powers was introduced to</t>
+          <t>The judiciary in India is independent because</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Avoid concentration of power</t>
+          <t>Judges have security of tenure</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Ensure efficiency</t>
+          <t>Judges are appointed by Parliament</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Promote unity</t>
+          <t>Judges can be removed easily</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Centralize authority</t>
+          <t>Judges report to Executive</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Avoid concentration of power</t>
+          <t>Judges have security of tenure</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Prevents abuse of power.</t>
+          <t>Ensures impartial decisions.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>25</v>
+        <v>63</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Separation of powers helps in</t>
+          <t>Which organ approves the budget?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Consolidating power</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Democracy and accountability</t>
+          <t>Legislature</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dictatorship</t>
+          <t>Judiciary</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Political stability only</t>
+          <t>Finance Commission</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Democracy and accountability</t>
+          <t>Legislature</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Ensures balanced governance.</t>
+          <t>Parliament approves government budget.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>37</v>
+        <v>89</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Separation of powers ensures</t>
+          <t>The independence of judiciary in India is protected by</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Concentration of power</t>
+          <t>Security of tenure and fixed salaries</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Checks and balances</t>
+          <t>Appointment by Legislature</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Conflicts among organs</t>
+          <t>Removal by Executive</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Political deadlock</t>
+          <t>Approval by Parliament</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Checks and balances</t>
+          <t>Security of tenure and fixed salaries</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Prevents abuse of power.</t>
+          <t>Ensures impartial judiciary.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>99</v>
+        <v>22</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Which organ appoints the Prime Minister?</t>
+          <t>Legislative power in India</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Is exercised by Parliament</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Is exercised by President alone</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Is exercised by Judiciary</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Chief Justice</t>
+          <t>Is exercised by Executive alone</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Is exercised by Parliament</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>President appoints PM who commands majority.</t>
+          <t>Parliament legislates laws.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Which Article in Indian Constitution provides for the separation of judiciary from executive?</t>
+          <t>Who is called the ‘Guardian of the Constitution’?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Article 50</t>
+          <t>President</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Article 51</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Article 44</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Article 52</t>
+          <t>Attorney General</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Article 50</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Directive Principle for judicial independence.</t>
+          <t>Protects constitutional rights.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Who is called the ‘Guardian of the Constitution’?</t>
+          <t>Which Article in Indian Constitution provides for the separation of judiciary from executive?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Article 50</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Article 51</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Article 44</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Attorney General</t>
+          <t>Article 52</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Article 50</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Protects constitutional rights.</t>
+          <t>Directive Principle for judicial independence.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>22</v>
+        <v>99</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Legislative power in India</t>
+          <t>Which organ appoints the Prime Minister?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Is exercised by Parliament</t>
+          <t>President</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Is exercised by President alone</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Is exercised by Judiciary</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Is exercised by Executive alone</t>
+          <t>Chief Justice</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Is exercised by Parliament</t>
+          <t>President</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Parliament legislates laws.</t>
+          <t>President appoints PM who commands majority.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>89</v>
+        <v>37</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>The independence of judiciary in India is protected by</t>
+          <t>Separation of powers ensures</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Security of tenure and fixed salaries</t>
+          <t>Concentration of power</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Appointment by Legislature</t>
+          <t>Checks and balances</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Removal by Executive</t>
+          <t>Conflicts among organs</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Approval by Parliament</t>
+          <t>Political deadlock</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Security of tenure and fixed salaries</t>
+          <t>Checks and balances</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Ensures impartial judiciary.</t>
+          <t>Prevents abuse of power.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>63</v>
+        <v>25</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Which organ approves the budget?</t>
+          <t>Separation of powers helps in</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Executive</t>
+          <t>Consolidating power</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Legislature</t>
+          <t>Democracy and accountability</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Judiciary</t>
+          <t>Dictatorship</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Finance Commission</t>
+          <t>Political stability only</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Legislature</t>
+          <t>Democracy and accountability</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Parliament approves government budget.</t>
+          <t>Ensures balanced governance.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>The judiciary in India is independent because</t>
+          <t>The doctrine of separation of powers was introduced to</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Judges have security of tenure</t>
+          <t>Avoid concentration of power</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Judges are appointed by Parliament</t>
+          <t>Ensure efficiency</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Judges can be removed easily</t>
+          <t>Promote unity</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Judges report to Executive</t>
+          <t>Centralize authority</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Judges have security of tenure</t>
+          <t>Avoid concentration of power</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Ensures impartial decisions.</t>
+          <t>Prevents abuse of power.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Who said “Power tends to corrupt, and absolute power corrupts absolutely”?</t>
+          <t>The President of India is part of which organ?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Montesquieu</t>
+          <t>Executive only</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Lord Acton</t>
+          <t>Legislature only</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>John Locke</t>
+          <t>Both Executive and Legislature</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>James Madison</t>
+          <t>Judiciary</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lord Acton</t>
+          <t>Both Executive and Legislature</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Warned about concentration of power.</t>
+          <t>President is head of Executive and Parliament.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>The power to issue ordinances lies with</t>
+          <t>Which principle limits the powers of government organs?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Judicial Activism</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Separation of Powers</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Federalism</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Universal Adult Franchise</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Separation of Powers</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>President can promulgate ordinances.</t>
+          <t>Divides power among branches.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Which organ has the power to amend the Constitution?</t>
+          <t>The power to promulgate ordinances rests with</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Judiciary</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Executive</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Speaker of Lok Sabha</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
+          <t>Chief Justice</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
           <t>President</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Parliament</t>
-        </is>
-      </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Legislature can amend Constitution under Article 368.</t>
+          <t>Under Article 123, President can issue ordinances.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>The term ‘checks and balances’ means</t>
+          <t>In India, the Supreme Court acts as a</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Each organ checks the other’s powers</t>
+          <t>Legislature</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>All powers are in one organ</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Judiciary controls all</t>
+          <t>Guardian of the Constitution</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Executive controls Legislature</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Each organ checks the other’s powers</t>
+          <t>Guardian of the Constitution</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Prevents power abuse.</t>
+          <t>It protects constitutional rights.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>45</v>
+        <v>85</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>The system where powers overlap but are balanced is called</t>
+          <t>The power of the Judiciary to review the Constitutionality of a law is called</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Fusion of Powers</t>
+          <t>Judicial review</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Separation of Powers</t>
+          <t>Judicial activism</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Partial Fusion</t>
+          <t>Judicial restraint</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Checks and Balances</t>
+          <t>Judicial supremacy</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Checks and Balances</t>
+          <t>Judicial review</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Ensures mutual accountability.</t>
+          <t>A key feature of Indian judiciary.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>85</v>
+        <v>45</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>The power of the Judiciary to review the Constitutionality of a law is called</t>
+          <t>The system where powers overlap but are balanced is called</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Judicial review</t>
+          <t>Fusion of Powers</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Judicial activism</t>
+          <t>Separation of Powers</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Judicial restraint</t>
+          <t>Partial Fusion</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Judicial supremacy</t>
+          <t>Checks and Balances</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Judicial review</t>
+          <t>Checks and Balances</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>A key feature of Indian judiciary.</t>
+          <t>Ensures mutual accountability.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>In India, the Supreme Court acts as a</t>
+          <t>The term ‘checks and balances’ means</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Legislature</t>
+          <t>Each organ checks the other’s powers</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Executive</t>
+          <t>All powers are in one organ</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Guardian of the Constitution</t>
+          <t>Judiciary controls all</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Executive controls Legislature</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Guardian of the Constitution</t>
+          <t>Each organ checks the other’s powers</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>It protects constitutional rights.</t>
+          <t>Prevents power abuse.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>The power to promulgate ordinances rests with</t>
+          <t>Which organ has the power to amend the Constitution?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Judiciary</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
+          <t>Executive</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Parliament</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
           <t>President</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Speaker of Lok Sabha</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Chief Justice</t>
-        </is>
-      </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Under Article 123, President can issue ordinances.</t>
+          <t>Legislature can amend Constitution under Article 368.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Which principle limits the powers of government organs?</t>
+          <t>The power to issue ordinances lies with</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Judicial Activism</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Separation of Powers</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Federalism</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Universal Adult Franchise</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Separation of Powers</t>
+          <t>President</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Divides power among branches.</t>
+          <t>President can promulgate ordinances.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>The President of India is part of which organ?</t>
+          <t>Who said “Power tends to corrupt, and absolute power corrupts absolutely”?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Executive only</t>
+          <t>Montesquieu</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Legislature only</t>
+          <t>Lord Acton</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Both Executive and Legislature</t>
+          <t>John Locke</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Judiciary</t>
+          <t>James Madison</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Both Executive and Legislature</t>
+          <t>Lord Acton</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>President is head of Executive and Parliament.</t>
+          <t>Warned about concentration of power.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>73</v>
+        <v>5</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Which organ is responsible for framing the policies of the government?</t>
+          <t>Which branch implements the laws?</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1706,337 +1706,337 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Executes and formulates policies.</t>
+          <t>Responsible for enforcing laws.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>78</v>
+        <v>17</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Which of the following is a check by the Legislature on the Executive?</t>
+          <t>The Executive</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Judicial Review</t>
+          <t>Can veto laws</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Vote of No-Confidence</t>
+          <t>Enforces laws</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ordinance Power</t>
+          <t>Interprets laws</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Appointment of Judges</t>
+          <t>Both a and c</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Vote of No-Confidence</t>
+          <t>Enforces laws</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Legislature can remove the government by this motion.</t>
+          <t>Executes and administers laws.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>In Indian Constitution, which organ has the power to dissolve the Lok Sabha?</t>
+          <t>Which of the following is NOT a function of the Executive?</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Implementing laws</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Making laws</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Chief Justice</t>
+          <t>Administering policies</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Maintaining public order</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Making laws</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>On advice of Prime Minister.</t>
+          <t>Lawmaking is primarily Legislature's function.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Who ensures that the Executive functions according to the law?</t>
+          <t>Which organ of the government is known as the ‘sword arm’ of the state?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
+          <t>Legislature</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Executive</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
           <t>Judiciary</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Legislature</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>President</t>
-        </is>
-      </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Press</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Judiciary</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Through judicial review and writ jurisdiction.</t>
+          <t>The Executive enforces laws and maintains order.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Who is the head of the Legislature in India?</t>
+          <t>What is the doctrine of Separation of Powers?</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Division of government powers among Legislature, Executive, Judiciary</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Sharing powers among political parties</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Speaker of Lok Sabha</t>
+          <t>Concentration of power in one organ</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Chief Justice</t>
+          <t>Division of powers between Centre and State</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Division of government powers among Legislature, Executive, Judiciary</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>He is the head of Parliament.</t>
+          <t>It means each branch has distinct functions.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>What is the doctrine of Separation of Powers?</t>
+          <t>Who is the head of the Legislature in India?</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Division of government powers among Legislature, Executive, Judiciary</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Sharing powers among political parties</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Concentration of power in one organ</t>
+          <t>Speaker of Lok Sabha</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Division of powers between Centre and State</t>
+          <t>Chief Justice</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Division of government powers among Legislature, Executive, Judiciary</t>
+          <t>President</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>It means each branch has distinct functions.</t>
+          <t>He is the head of Parliament.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Which organ of the government is known as the ‘sword arm’ of the state?</t>
+          <t>Who ensures that the Executive functions according to the law?</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
+          <t>Judiciary</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
           <t>Legislature</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Executive</t>
-        </is>
-      </c>
       <c r="E38" t="inlineStr">
         <is>
+          <t>President</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Prime Minister</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
           <t>Judiciary</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Press</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Executive</t>
-        </is>
-      </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>The Executive enforces laws and maintains order.</t>
+          <t>Through judicial review and writ jurisdiction.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Which of the following is NOT a function of the Executive?</t>
+          <t>In Indian Constitution, which organ has the power to dissolve the Lok Sabha?</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Implementing laws</t>
+          <t>President</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Making laws</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Administering policies</t>
+          <t>Chief Justice</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Maintaining public order</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Making laws</t>
+          <t>President</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Lawmaking is primarily Legislature's function.</t>
+          <t>On advice of Prime Minister.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>17</v>
+        <v>78</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>The Executive</t>
+          <t>Which of the following is a check by the Legislature on the Executive?</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Can veto laws</t>
+          <t>Judicial Review</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Enforces laws</t>
+          <t>Vote of No-Confidence</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Interprets laws</t>
+          <t>Ordinance Power</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Both a and c</t>
+          <t>Appointment of Judges</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Enforces laws</t>
+          <t>Vote of No-Confidence</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Executes and administers laws.</t>
+          <t>Legislature can remove the government by this motion.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>5</v>
+        <v>73</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Which branch implements the laws?</t>
+          <t>Which organ is responsible for framing the policies of the government?</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2066,597 +2066,597 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Responsible for enforcing laws.</t>
+          <t>Executes and formulates policies.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>12</v>
+        <v>70</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Who appoints the Chief Justice of India?</t>
+          <t>Which of the following best describes the Indian model of separation of powers?</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Absolute and rigid separation</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Flexible and overlapping powers</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Complete fusion</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Supreme Court Judges</t>
+          <t>No separation</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Flexible and overlapping powers</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>The President appoints CJI.</t>
+          <t>Allows cooperation with checks.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Who holds the power to dissolve the Lok Sabha?</t>
+          <t>Judiciary independence is protected by</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Fixed tenure of judges</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Security of tenure</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Speaker of Lok Sabha</t>
+          <t>Independence of appointment</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Chief Justice of India</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Dissolution is done by the President on PM's advice.</t>
+          <t>Ensures impartial judiciary.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>91</v>
+        <v>56</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Which organ controls the government expenditure?</t>
+          <t>The President’s power to summon and prorogue Parliament is part of</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Executive</t>
+          <t>Executive powers</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Legislature</t>
+          <t>Legislative powers</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Judiciary</t>
+          <t>Judicial powers</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Finance Commission</t>
+          <t>Financial powers</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Legislature</t>
+          <t>Legislative powers</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Parliament controls budget.</t>
+          <t>President as part of Parliament exercises these powers.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Which article of the Indian Constitution mentions separation of powers explicitly?</t>
+          <t>The power of the Executive to reject laws passed by Legislature is called</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Article 50</t>
+          <t>Judicial Review</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Article 368</t>
+          <t>Veto Power</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Article 14</t>
+          <t>Ordinance Power</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>No article</t>
+          <t>Amendment Power</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>No article</t>
+          <t>Veto Power</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>It is implied, not explicitly mentioned.</t>
+          <t>President can veto bills.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>18</v>
+        <v>65</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>The Judiciary</t>
+          <t>Which case established the power of judicial review in India?</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Declares laws unconstitutional</t>
+          <t>Kesavananda Bharati</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Enforces laws</t>
+          <t>Golaknath</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Makes laws</t>
+          <t>Marbury v Madison</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Both a and c</t>
+          <t>Minerva Mills</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Declares laws unconstitutional</t>
+          <t>Kesavananda Bharati</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Protects constitutionality.</t>
+          <t>It upheld the basic structure doctrine.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>65</v>
+        <v>18</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Which case established the power of judicial review in India?</t>
+          <t>The Judiciary</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Kesavananda Bharati</t>
+          <t>Declares laws unconstitutional</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Golaknath</t>
+          <t>Enforces laws</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Marbury v Madison</t>
+          <t>Makes laws</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Minerva Mills</t>
+          <t>Both a and c</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Kesavananda Bharati</t>
+          <t>Declares laws unconstitutional</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>It upheld the basic structure doctrine.</t>
+          <t>Protects constitutionality.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>The power of the Executive to reject laws passed by Legislature is called</t>
+          <t>Which article of the Indian Constitution mentions separation of powers explicitly?</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Judicial Review</t>
+          <t>Article 50</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Veto Power</t>
+          <t>Article 368</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Ordinance Power</t>
+          <t>Article 14</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Amendment Power</t>
+          <t>No article</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Veto Power</t>
+          <t>No article</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>President can veto bills.</t>
+          <t>It is implied, not explicitly mentioned.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>56</v>
+        <v>91</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>The President’s power to summon and prorogue Parliament is part of</t>
+          <t>Which organ controls the government expenditure?</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Executive powers</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Legislative powers</t>
+          <t>Legislature</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Judicial powers</t>
+          <t>Judiciary</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Financial powers</t>
+          <t>Finance Commission</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Legislative powers</t>
+          <t>Legislature</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>President as part of Parliament exercises these powers.</t>
+          <t>Parliament controls budget.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>24</v>
+        <v>77</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Judiciary independence is protected by</t>
+          <t>Who holds the power to dissolve the Lok Sabha?</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Fixed tenure of judges</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Security of tenure</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Independence of appointment</t>
+          <t>Speaker of Lok Sabha</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Chief Justice of India</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>President</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Ensures impartial judiciary.</t>
+          <t>Dissolution is done by the President on PM's advice.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>70</v>
+        <v>12</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Which of the following best describes the Indian model of separation of powers?</t>
+          <t>Who appoints the Chief Justice of India?</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Absolute and rigid separation</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Flexible and overlapping powers</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Complete fusion</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>No separation</t>
+          <t>Supreme Court Judges</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Flexible and overlapping powers</t>
+          <t>President</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Allows cooperation with checks.</t>
+          <t>The President appoints CJI.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>54</v>
+        <v>11</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Which constitutional article mandates the separation of judiciary from executive in India?</t>
+          <t>Judicial review is an example of</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Article 50</t>
+          <t>Judiciary checking Legislature</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Article 44</t>
+          <t>Executive controlling Judiciary</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Article 37</t>
+          <t>Legislature controlling Executive</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Article 51</t>
+          <t>Legislature checking Judiciary</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Article 50</t>
+          <t>Judiciary checking Legislature</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Part of DPSP, directs separation for judicial independence.</t>
+          <t>Ensures laws are constitutional.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Which organ enforces the laws in India?</t>
+          <t>Which organ is responsible for enforcing laws?</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
+          <t>Legislature</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Executive</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
           <t>Judiciary</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Both Legislature and Judiciary</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
         <is>
           <t>Executive</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>Legislature</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>None of the above</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>Executive</t>
-        </is>
-      </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>The executive implements laws.</t>
+          <t>Executes laws.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>The judiciary can</t>
+          <t>The Cabinet is part of which organ?</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Strike down unconstitutional laws</t>
+          <t>Legislature</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Pass budgets</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Execute laws</t>
+          <t>Judiciary</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Make treaties</t>
+          <t>None of the above</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Strike down unconstitutional laws</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>It safeguards Constitution.</t>
+          <t>It is the real decision-making body of Executive.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>61</v>
+        <v>29</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Which body can impeach a Supreme Court judge?</t>
+          <t>The Indian Constitution follows which kind of separation of powers?</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Strict Separation</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Partial Separation</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Chief Justice</t>
+          <t>No Separation</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Complete Merger</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Partial Separation</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Parliament initiates impeachment proceedings.</t>
+          <t>Separation with checks and balances.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Which body checks the actions of the Executive?</t>
+          <t>Which branch interprets the laws?</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
+          <t>Legislature</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Executive</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
           <t>Judiciary</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>Legislature</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>Press</t>
-        </is>
-      </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Military</t>
+          <t>Police</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -2666,1799 +2666,1799 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Judicial review controls Executive excess.</t>
+          <t>Courts interpret laws.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Which branch interprets the laws?</t>
+          <t>Which body checks the actions of the Executive?</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
+          <t>Judiciary</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
           <t>Legislature</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>Executive</t>
-        </is>
-      </c>
       <c r="E57" t="inlineStr">
         <is>
+          <t>Press</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Military</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
           <t>Judiciary</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Police</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>Judiciary</t>
-        </is>
-      </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Courts interpret laws.</t>
+          <t>Judicial review controls Executive excess.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>29</v>
+        <v>61</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>The Indian Constitution follows which kind of separation of powers?</t>
+          <t>Which body can impeach a Supreme Court judge?</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Strict Separation</t>
+          <t>President</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Partial Separation</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>No Separation</t>
+          <t>Chief Justice</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Complete Merger</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Partial Separation</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Separation with checks and balances.</t>
+          <t>Parliament initiates impeachment proceedings.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>The Cabinet is part of which organ?</t>
+          <t>The judiciary can</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Legislature</t>
+          <t>Strike down unconstitutional laws</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Executive</t>
+          <t>Pass budgets</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Judiciary</t>
+          <t>Execute laws</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>None of the above</t>
+          <t>Make treaties</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Executive</t>
+          <t>Strike down unconstitutional laws</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>It is the real decision-making body of Executive.</t>
+          <t>It safeguards Constitution.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Which organ is responsible for enforcing laws?</t>
+          <t>Which organ enforces the laws in India?</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
+          <t>Judiciary</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Executive</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
           <t>Legislature</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>None of the above</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
         <is>
           <t>Executive</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>Judiciary</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>Both Legislature and Judiciary</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>Executive</t>
-        </is>
-      </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Executes laws.</t>
+          <t>The executive implements laws.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>11</v>
+        <v>54</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Judicial review is an example of</t>
+          <t>Which constitutional article mandates the separation of judiciary from executive in India?</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Judiciary checking Legislature</t>
+          <t>Article 50</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Executive controlling Judiciary</t>
+          <t>Article 44</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Legislature controlling Executive</t>
+          <t>Article 37</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Legislature checking Judiciary</t>
+          <t>Article 51</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Judiciary checking Legislature</t>
+          <t>Article 50</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Ensures laws are constitutional.</t>
+          <t>Part of DPSP, directs separation for judicial independence.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>44</v>
+        <v>100</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>In India, which organ controls the budget?</t>
+          <t>Which article defines the powers of the Supreme Court?</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Executive</t>
+          <t>Article 124</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Legislature</t>
+          <t>Article 217</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Judiciary</t>
+          <t>Article 50</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Press</t>
+          <t>Article 368</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Legislature</t>
+          <t>Article 124</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Parliament controls financial powers.</t>
+          <t>Details appointment and jurisdiction.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>4</v>
+        <v>72</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Which branch makes laws according to the doctrine of separation of powers?</t>
+          <t>Which principle states that no one should exercise the powers of more than one branch?</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Executive</t>
+          <t>Checks and balances</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Judiciary</t>
+          <t>Separation of Powers</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Legislature</t>
+          <t>Federalism</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Police</t>
+          <t>Rule of Law</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Legislature</t>
+          <t>Separation of Powers</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Legislature enacts laws.</t>
+          <t>Ensures distinct roles.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>74</v>
+        <v>33</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Who is the constitutional head of the Executive in India?</t>
+          <t>Judicial review in India is exercised by</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Supreme Court only</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>High Courts only</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Chief Justice</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Governor</t>
-        </is>
-      </c>
+          <t>Both Supreme Court and High Courts</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Both Supreme Court and High Courts</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Nominal head of the Executive.</t>
+          <t>Both levels have power of judicial review.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>64</v>
+        <v>92</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>The power of judicial review is derived from</t>
+          <t>The power to promulgate ordinances is vested in</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Written Constitution</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Unwritten conventions</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Parliamentary resolutions</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Presidential orders</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Written Constitution</t>
+          <t>President</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Explicitly or implicitly provided in the Constitution.</t>
+          <t>Under Article 123.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Who said “Power corrupts; absolute power corrupts absolutely”?</t>
+          <t>Which case declared that the basic structure of the Constitution cannot be altered by Parliament?</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Montesquieu</t>
+          <t>Kesavananda Bharati</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>John Locke</t>
+          <t>Golaknath</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Lord Acton</t>
+          <t>Minerva Mills</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Jean-Jacques Rousseau</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lord Acton</t>
+          <t>Kesavananda Bharati</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>A famous quote on power abuse.</t>
+          <t>The landmark basic structure doctrine case.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Which case declared that the basic structure of the Constitution cannot be altered by Parliament?</t>
+          <t>Who said “Power corrupts; absolute power corrupts absolutely”?</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Kesavananda Bharati</t>
+          <t>Montesquieu</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Golaknath</t>
+          <t>John Locke</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Minerva Mills</t>
+          <t>Lord Acton</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Jean-Jacques Rousseau</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Kesavananda Bharati</t>
+          <t>Lord Acton</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>The landmark basic structure doctrine case.</t>
+          <t>A famous quote on power abuse.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>92</v>
+        <v>64</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>The power to promulgate ordinances is vested in</t>
+          <t>The power of judicial review is derived from</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Written Constitution</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Unwritten conventions</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Parliamentary resolutions</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Presidential orders</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Written Constitution</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Under Article 123.</t>
+          <t>Explicitly or implicitly provided in the Constitution.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>33</v>
+        <v>74</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Judicial review in India is exercised by</t>
+          <t>Who is the constitutional head of the Executive in India?</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Supreme Court only</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>High Courts only</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Both Supreme Court and High Courts</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr"/>
+          <t>Chief Justice</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Both Supreme Court and High Courts</t>
+          <t>President</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Both levels have power of judicial review.</t>
+          <t>Nominal head of the Executive.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>72</v>
+        <v>4</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Which principle states that no one should exercise the powers of more than one branch?</t>
+          <t>Which branch makes laws according to the doctrine of separation of powers?</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Checks and balances</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Separation of Powers</t>
+          <t>Judiciary</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Federalism</t>
+          <t>Legislature</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rule of Law</t>
+          <t>Police</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Separation of Powers</t>
+          <t>Legislature</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Ensures distinct roles.</t>
+          <t>Legislature enacts laws.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>100</v>
+        <v>44</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Which article defines the powers of the Supreme Court?</t>
+          <t>In India, which organ controls the budget?</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Article 124</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Article 217</t>
+          <t>Legislature</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Article 50</t>
+          <t>Judiciary</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Article 368</t>
+          <t>Press</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Article 124</t>
+          <t>Legislature</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Details appointment and jurisdiction.</t>
+          <t>Parliament controls financial powers.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>98</v>
+        <v>38</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>The President of India acts on the advice of</t>
+          <t>Which organ interprets the Constitution?</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Prime Minister and Council of Ministers</t>
+          <t>Legislature</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Judiciary</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Speaker of Lok Sabha</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Prime Minister and Council of Ministers</t>
+          <t>Judiciary</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>The real executive authority lies with them.</t>
+          <t>Courts interpret laws and Constitution.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>9</v>
+        <v>83</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>The Executive in India is responsible to</t>
+          <t>The President of India is part of which organs?</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>The President</t>
+          <t>Executive only</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>The Judiciary</t>
+          <t>Legislature only</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>The Parliament</t>
+          <t>Both Executive and Legislature</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>The Police</t>
+          <t>Judiciary</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>The Parliament</t>
+          <t>Both Executive and Legislature</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>It is responsible to the legislature.</t>
+          <t>President is constitutional head of both.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>53</v>
+        <v>81</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>The power of the Legislature to check the Executive is exercised through</t>
+          <t>Which organ of the government is responsible for implementing laws?</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>No-confidence motion</t>
+          <t>Legislature</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Judicial review</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Ordinance power</t>
+          <t>Judiciary</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Amendment power</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>No-confidence motion</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>It can remove the government by vote of no-confidence.</t>
+          <t>The executive enforces the laws.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Which organ of government appoints judges in India?</t>
+          <t>The principle of Separation of Powers helps to</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Legislature</t>
+          <t>Prevent misuse of power</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Executive</t>
+          <t>Concentrate power</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Judiciary itself</t>
+          <t>Make laws faster</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>President on recommendation</t>
+          <t>Increase political parties</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>President on recommendation</t>
+          <t>Prevent misuse of power</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>President appoints judges on recommendations.</t>
+          <t>Avoids arbitrary rule.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>26</v>
+        <v>82</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Which of the following is NOT a basic feature of the Indian Constitution?</t>
+          <t>Judicial review means</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Separation of Powers</t>
+          <t>Making laws</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Federalism</t>
+          <t>Interpreting laws and declaring laws unconstitutional</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Judicial Review</t>
+          <t>Enforcing laws</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Absolute Separation of Powers</t>
+          <t>Approving budget</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Absolute Separation of Powers</t>
+          <t>Interpreting laws and declaring laws unconstitutional</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>India follows partial separation, not absolute.</t>
+          <t>Ensures laws comply with Constitution.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>82</v>
+        <v>26</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Judicial review means</t>
+          <t>Which of the following is NOT a basic feature of the Indian Constitution?</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Making laws</t>
+          <t>Separation of Powers</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Interpreting laws and declaring laws unconstitutional</t>
+          <t>Federalism</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Enforcing laws</t>
+          <t>Judicial Review</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Approving budget</t>
+          <t>Absolute Separation of Powers</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Interpreting laws and declaring laws unconstitutional</t>
+          <t>Absolute Separation of Powers</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Ensures laws comply with Constitution.</t>
+          <t>India follows partial separation, not absolute.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>The principle of Separation of Powers helps to</t>
+          <t>Which organ of government appoints judges in India?</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Prevent misuse of power</t>
+          <t>Legislature</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Concentrate power</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Make laws faster</t>
+          <t>Judiciary itself</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Increase political parties</t>
+          <t>President on recommendation</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Prevent misuse of power</t>
+          <t>President on recommendation</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Avoids arbitrary rule.</t>
+          <t>President appoints judges on recommendations.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>81</v>
+        <v>53</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Which organ of the government is responsible for implementing laws?</t>
+          <t>The power of the Legislature to check the Executive is exercised through</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Legislature</t>
+          <t>No-confidence motion</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Executive</t>
+          <t>Judicial review</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Judiciary</t>
+          <t>Ordinance power</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Amendment power</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Executive</t>
+          <t>No-confidence motion</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>The executive enforces the laws.</t>
+          <t>It can remove the government by vote of no-confidence.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>83</v>
+        <v>9</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>The President of India is part of which organs?</t>
+          <t>The Executive in India is responsible to</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Executive only</t>
+          <t>The President</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Legislature only</t>
+          <t>The Judiciary</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Both Executive and Legislature</t>
+          <t>The Parliament</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Judiciary</t>
+          <t>The Police</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Both Executive and Legislature</t>
+          <t>The Parliament</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>President is constitutional head of both.</t>
+          <t>It is responsible to the legislature.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>38</v>
+        <v>98</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Which organ interprets the Constitution?</t>
+          <t>The President of India acts on the advice of</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Legislature</t>
+          <t>Prime Minister and Council of Ministers</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Executive</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Judiciary</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Speaker of Lok Sabha</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Judiciary</t>
+          <t>Prime Minister and Council of Ministers</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Courts interpret laws and Constitution.</t>
+          <t>The real executive authority lies with them.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>97</v>
+        <v>21</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>The principle of Separation of Powers aims at</t>
+          <t>The separation of powers in India is</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Centralization of power</t>
+          <t>Strict</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Distribution of powers</t>
+          <t>Flexible</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Concentration of power</t>
+          <t>Absent</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Merger of powers</t>
+          <t>Unconstitutional</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Distribution of powers</t>
+          <t>Flexible</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Avoids power concentration.</t>
+          <t>Allows cooperation among branches.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Which is a feature of partial separation of powers in India?</t>
+          <t>Which Article of the Indian Constitution provides for the appointment of the Chief Justice of India?</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Judges can be executive officers</t>
+          <t>Article 124</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Legislature controls Judiciary</t>
+          <t>Article 217</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Executive is responsible to Legislature</t>
+          <t>Article 50</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>No checks and balances</t>
+          <t>Article 368</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Executive is responsible to Legislature</t>
+          <t>Article 124</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Shows overlap but with accountability.</t>
+          <t>Provides appointment procedure.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>15</v>
+        <v>95</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Who suggested the idea of separation of powers in Indian Constitution drafting?</t>
+          <t>The executive is responsible to</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>B.R. Ambedkar</t>
+          <t>Legislature</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Mahatma Gandhi</t>
+          <t>Judiciary</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Jawaharlal Nehru</t>
+          <t>President</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>All of them</t>
+          <t>Election Commission</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>B.R. Ambedkar</t>
+          <t>Legislature</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>He explained doctrine in the Constituent Assembly.</t>
+          <t>Executive is accountable to Parliament.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>94</v>
+        <v>27</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>In India, the power to amend the Constitution lies with</t>
+          <t>Which organ has the power to make laws in India?</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Judiciary</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Judiciary</t>
+          <t>Legislature</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Legislature</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Under Article 368.</t>
+          <t>Legislature makes laws.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Who holds the real executive power in India?</t>
+          <t>Which of the following cases emphasized the importance of separation of powers?</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Kesavananda Bharati</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Prime Minister and Council of Ministers</t>
+          <t>Minerva Mills</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Golak Nath</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Indira Gandhi Case</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Prime Minister and Council of Ministers</t>
+          <t>Kesavananda Bharati</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>They hold actual power.</t>
+          <t>Upheld basic structure doctrine including separation of powers.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Which of the following cases emphasized the importance of separation of powers?</t>
+          <t>Who holds the real executive power in India?</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Kesavananda Bharati</t>
+          <t>President</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Minerva Mills</t>
+          <t>Prime Minister and Council of Ministers</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Golak Nath</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Indira Gandhi Case</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Kesavananda Bharati</t>
+          <t>Prime Minister and Council of Ministers</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Upheld basic structure doctrine including separation of powers.</t>
+          <t>They hold actual power.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>27</v>
+        <v>94</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Which organ has the power to make laws in India?</t>
+          <t>In India, the power to amend the Constitution lies with</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
+          <t>Parliament</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>President</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
           <t>Judiciary</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>Executive</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>Legislature</t>
-        </is>
-      </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Legislature</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Legislature makes laws.</t>
+          <t>Under Article 368.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>95</v>
+        <v>15</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>The executive is responsible to</t>
+          <t>Who suggested the idea of separation of powers in Indian Constitution drafting?</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Legislature</t>
+          <t>B.R. Ambedkar</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Judiciary</t>
+          <t>Mahatma Gandhi</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Jawaharlal Nehru</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Election Commission</t>
+          <t>All of them</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Legislature</t>
+          <t>B.R. Ambedkar</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Executive is accountable to Parliament.</t>
+          <t>He explained doctrine in the Constituent Assembly.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Which Article of the Indian Constitution provides for the appointment of the Chief Justice of India?</t>
+          <t>Which is a feature of partial separation of powers in India?</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Article 124</t>
+          <t>Judges can be executive officers</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Article 217</t>
+          <t>Legislature controls Judiciary</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Article 50</t>
+          <t>Executive is responsible to Legislature</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Article 368</t>
+          <t>No checks and balances</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Article 124</t>
+          <t>Executive is responsible to Legislature</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Provides appointment procedure.</t>
+          <t>Shows overlap but with accountability.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>21</v>
+        <v>97</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>The separation of powers in India is</t>
+          <t>The principle of Separation of Powers aims at</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Strict</t>
+          <t>Centralization of power</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Flexible</t>
+          <t>Distribution of powers</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Absent</t>
+          <t>Concentration of power</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Unconstitutional</t>
+          <t>Merger of powers</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Flexible</t>
+          <t>Distribution of powers</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Allows cooperation among branches.</t>
+          <t>Avoids power concentration.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>19</v>
+        <v>76</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Is there any overlap between powers in Indian system?</t>
+          <t>Which organ of government in India has the power to grant pardon and reprieve?</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Legislature</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Only in emergencies</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr"/>
+          <t>Judiciary</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>President</t>
+        </is>
+      </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Overlap exists but balanced by checks.</t>
+          <t>The President exercises this power as part of the executive.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>55</v>
+        <v>79</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>The principle of separation of powers helps in</t>
+          <t>Which body is responsible for appointing the judges of the High Courts?</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Avoiding dictatorship</t>
+          <t>President</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Encouraging dictatorship</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Centralizing power</t>
+          <t>Chief Justice of India and Governor</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Undermining democracy</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Avoiding dictatorship</t>
+          <t>Chief Justice of India and Governor</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Prevents concentration of power.</t>
+          <t>Appointment is made by President after consultation.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>14</v>
+        <v>88</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Which famous case discussed separation of powers and judicial independence?</t>
+          <t>Which of the following is a function of the Legislature?</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Kesavananda Bharati</t>
+          <t>Make laws</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Minerva Mills</t>
+          <t>Implement laws</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Interpret laws</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Golaknath</t>
+          <t>Enforce laws</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Minerva Mills</t>
+          <t>Make laws</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Emphasized balance between powers.</t>
+          <t>Lawmaking is the primary role.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>The Legislature can</t>
+          <t>Which organ enforces law and order?</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Make laws</t>
+          <t>Judiciary</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Enforce laws</t>
+          <t>Legislature</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Interpret laws</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>None of the above</t>
+          <t>Press</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Make laws</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Its primary function is lawmaking.</t>
+          <t>Police and administrative agencies.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>71</v>
+        <v>32</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Judges of the Supreme Court can be removed by</t>
+          <t>The doctrine of separation of powers was first developed by?</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Parliamentary impeachment</t>
+          <t>Montesquieu</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Presidential order</t>
+          <t>John Locke</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Executive decision</t>
+          <t>Thomas Hobbes</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Judicial verdict</t>
+          <t>Jean-Jacques Rousseau</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Parliamentary impeachment</t>
+          <t>Montesquieu</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Requires special majority in Parliament.</t>
+          <t>He introduced the concept.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>32</v>
+        <v>71</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>The doctrine of separation of powers was first developed by?</t>
+          <t>Judges of the Supreme Court can be removed by</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Montesquieu</t>
+          <t>Parliamentary impeachment</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>John Locke</t>
+          <t>Presidential order</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Thomas Hobbes</t>
+          <t>Executive decision</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Jean-Jacques Rousseau</t>
+          <t>Judicial verdict</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Montesquieu</t>
+          <t>Parliamentary impeachment</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>He introduced the concept.</t>
+          <t>Requires special majority in Parliament.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>96</v>
+        <v>16</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Which organ enforces law and order?</t>
+          <t>The Legislature can</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Judiciary</t>
+          <t>Make laws</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Legislature</t>
+          <t>Enforce laws</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Executive</t>
+          <t>Interpret laws</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Press</t>
+          <t>None of the above</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Executive</t>
+          <t>Make laws</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Police and administrative agencies.</t>
+          <t>Its primary function is lawmaking.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>88</v>
+        <v>14</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Which of the following is a function of the Legislature?</t>
+          <t>Which famous case discussed separation of powers and judicial independence?</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Make laws</t>
+          <t>Kesavananda Bharati</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Implement laws</t>
+          <t>Minerva Mills</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Interpret laws</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Enforce laws</t>
+          <t>Golaknath</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Make laws</t>
+          <t>Minerva Mills</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Lawmaking is the primary role.</t>
+          <t>Emphasized balance between powers.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Which body is responsible for appointing the judges of the High Courts?</t>
+          <t>The principle of separation of powers helps in</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Avoiding dictatorship</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Encouraging dictatorship</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Chief Justice of India and Governor</t>
+          <t>Centralizing power</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Undermining democracy</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Chief Justice of India and Governor</t>
+          <t>Avoiding dictatorship</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Appointment is made by President after consultation.</t>
+          <t>Prevents concentration of power.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>76</v>
+        <v>19</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Which organ of government in India has the power to grant pardon and reprieve?</t>
+          <t>Is there any overlap between powers in Indian system?</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Legislature</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Executive</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Judiciary</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>President</t>
-        </is>
-      </c>
+          <t>Only in emergencies</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Executive</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>The President exercises this power as part of the executive.</t>
+          <t>Overlap exists but balanced by checks.</t>
         </is>
       </c>
     </row>

--- a/Data/IP_SeperationofPower.xlsx
+++ b/Data/IP_SeperationofPower.xlsx
@@ -472,1171 +472,1167 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>46</v>
+        <v>13</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>The Indian Constitution provides for</t>
+          <t>Which is a feature of partial separation of powers in India?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Absolute separation of powers</t>
+          <t>Judges can be executive officers</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Partial separation with checks</t>
+          <t>Legislature controls Judiciary</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>No separation of powers</t>
+          <t>Executive is responsible to Legislature</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fusion of powers</t>
+          <t>No checks and balances</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Partial separation with checks</t>
+          <t>Executive is responsible to Legislature</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Balances power among organs.</t>
+          <t>Shows overlap but with accountability.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>87</v>
+        <v>24</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The executive in India is</t>
+          <t>Judiciary independence is protected by</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Constitutional and political</t>
+          <t>Fixed tenure of judges</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Absolute</t>
+          <t>Security of tenure</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Legislative</t>
+          <t>Independence of appointment</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Judicial</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Constitutional and political</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>It functions within constitutional limits.</t>
+          <t>Ensures impartial judiciary.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>The power to impeach the President lies with</t>
+          <t>Legislative power in India</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Is exercised by Parliament</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Is exercised by President alone</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Executive</t>
+          <t>Is exercised by Judiciary</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Constitutional Court</t>
+          <t>Is exercised by Executive alone</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Is exercised by Parliament</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Parliament initiates impeachment.</t>
+          <t>Parliament legislates laws.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>75</v>
+        <v>21</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>The Constitution of India was adopted in which year?</t>
+          <t>The separation of powers in India is</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1947</t>
+          <t>Strict</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1949</t>
+          <t>Flexible</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>Absent</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1952</t>
+          <t>Unconstitutional</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>Flexible</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Adopted on 26 January 1950.</t>
+          <t>Allows cooperation among branches.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2</v>
+        <v>91</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Who is known as the Father of the Doctrine of Separation of Powers?</t>
+          <t>Which organ controls the government expenditure?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>John Locke</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Montesquieu</t>
+          <t>Legislature</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Thomas Hobbes</t>
+          <t>Judiciary</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jean-Jacques Rousseau</t>
+          <t>Finance Commission</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Montesquieu</t>
+          <t>Legislature</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>He popularized the concept in “The Spirit of Laws”.</t>
+          <t>Parliament controls budget.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>68</v>
+        <v>18</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Which is the primary function of the Judiciary?</t>
+          <t>The Judiciary</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Make laws</t>
+          <t>Declares laws unconstitutional</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Enforce laws</t>
+          <t>Enforces laws</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Interpret laws</t>
+          <t>Makes laws</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Administer laws</t>
+          <t>Both a and c</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Interpret laws</t>
+          <t>Declares laws unconstitutional</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Judiciary interprets laws and Constitution.</t>
+          <t>Protects constitutionality.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Judicial independence in India is protected by</t>
+          <t>Which organ has the power to amend the Constitution?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Security of tenure</t>
+          <t>Judiciary</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Fixed salary</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Prohibition of arbitrary removal</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>President</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Ensures impartiality and fairness.</t>
+          <t>Legislature can amend Constitution under Article 368.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>The Legislature can</t>
+          <t>Who holds the power to dissolve the Lok Sabha?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Make laws</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Interpret laws</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Enforce laws</t>
+          <t>Speaker of Lok Sabha</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Chief Justice of India</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Make laws</t>
+          <t>President</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Its primary function is lawmaking.</t>
+          <t>Dissolution is done by the President on PM's advice.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Executive power flows from</t>
+          <t>The term ‘checks and balances’ means</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Legislature</t>
+          <t>Each organ checks the other’s powers</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Judiciary</t>
+          <t>All powers are in one organ</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Judiciary controls all</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Executive controls Legislature</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Each organ checks the other’s powers</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>The President is the nominal executive head.</t>
+          <t>Prevents power abuse.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>3</v>
+        <v>51</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>In the Indian Constitution, is the separation of powers absolute?</t>
+          <t>Which organ of the government is known as the ‘sword arm’ of the state?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Legislature</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Partially</t>
+          <t>Judiciary</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Press</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>India follows partial separation with checks and balances.</t>
+          <t>The Executive enforces laws and maintains order.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>39</v>
+        <v>5</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>The judiciary in India is independent because</t>
+          <t>Which branch implements the laws?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Judges have security of tenure</t>
+          <t>Legislature</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Judges are appointed by Parliament</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Judges can be removed easily</t>
+          <t>Judiciary</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Judges report to Executive</t>
+          <t>Press</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Judges have security of tenure</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Ensures impartial decisions.</t>
+          <t>Responsible for enforcing laws.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>63</v>
+        <v>1</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Which organ approves the budget?</t>
+          <t>What is the doctrine of Separation of Powers?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Executive</t>
+          <t>Division of government powers among Legislature, Executive, Judiciary</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Legislature</t>
+          <t>Sharing powers among political parties</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Judiciary</t>
+          <t>Concentration of power in one organ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Finance Commission</t>
+          <t>Division of powers between Centre and State</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Legislature</t>
+          <t>Division of government powers among Legislature, Executive, Judiciary</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Parliament approves government budget.</t>
+          <t>It means each branch has distinct functions.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>89</v>
+        <v>3</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>The independence of judiciary in India is protected by</t>
+          <t>In the Indian Constitution, is the separation of powers absolute?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Security of tenure and fixed salaries</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Appointment by Legislature</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Removal by Executive</t>
+          <t>Partially</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Approval by Parliament</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Security of tenure and fixed salaries</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Ensures impartial judiciary.</t>
+          <t>India follows partial separation with checks and balances.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Legislative power in India</t>
+          <t>Which organ has the power to make laws in India?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Is exercised by Parliament</t>
+          <t>Judiciary</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Is exercised by President alone</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Is exercised by Judiciary</t>
+          <t>Legislature</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Is exercised by Executive alone</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Is exercised by Parliament</t>
+          <t>Legislature</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Parliament legislates laws.</t>
+          <t>Legislature makes laws.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>93</v>
+        <v>68</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Who is called the ‘Guardian of the Constitution’?</t>
+          <t>Which is the primary function of the Judiciary?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Make laws</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Enforce laws</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Interpret laws</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Attorney General</t>
+          <t>Administer laws</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Interpret laws</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Protects constitutional rights.</t>
+          <t>Judiciary interprets laws and Constitution.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>84</v>
+        <v>33</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Which Article in Indian Constitution provides for the separation of judiciary from executive?</t>
+          <t>Judicial review in India is exercised by</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Article 50</t>
+          <t>Supreme Court only</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Article 51</t>
+          <t>High Courts only</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Article 44</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Article 52</t>
-        </is>
-      </c>
+          <t>Both Supreme Court and High Courts</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Article 50</t>
+          <t>Both Supreme Court and High Courts</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Directive Principle for judicial independence.</t>
+          <t>Both levels have power of judicial review.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Which organ appoints the Prime Minister?</t>
+          <t>Which Article in Indian Constitution provides for the separation of judiciary from executive?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Article 50</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Article 51</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Article 44</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Chief Justice</t>
+          <t>Article 52</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Article 50</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>President appoints PM who commands majority.</t>
+          <t>Directive Principle for judicial independence.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>37</v>
+        <v>69</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Separation of powers ensures</t>
+          <t>In Indian Constitution, which organ has the power to dissolve the Lok Sabha?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Concentration of power</t>
+          <t>President</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Checks and balances</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Conflicts among organs</t>
+          <t>Chief Justice</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Political deadlock</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Checks and balances</t>
+          <t>President</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Prevents abuse of power.</t>
+          <t>On advice of Prime Minister.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>25</v>
+        <v>52</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Separation of powers helps in</t>
+          <t>Who ensures that the Executive functions according to the law?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Consolidating power</t>
+          <t>Judiciary</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Democracy and accountability</t>
+          <t>Legislature</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Dictatorship</t>
+          <t>President</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Political stability only</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Democracy and accountability</t>
+          <t>Judiciary</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Ensures balanced governance.</t>
+          <t>Through judicial review and writ jurisdiction.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>80</v>
+        <v>11</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>The doctrine of separation of powers was introduced to</t>
+          <t>Judicial review is an example of</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Avoid concentration of power</t>
+          <t>Judiciary checking Legislature</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Ensure efficiency</t>
+          <t>Executive controlling Judiciary</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Promote unity</t>
+          <t>Legislature controlling Executive</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Centralize authority</t>
+          <t>Legislature checking Judiciary</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Avoid concentration of power</t>
+          <t>Judiciary checking Legislature</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Prevents abuse of power.</t>
+          <t>Ensures laws are constitutional.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>The President of India is part of which organ?</t>
+          <t>The judiciary can</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Executive only</t>
+          <t>Strike down unconstitutional laws</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Legislature only</t>
+          <t>Pass budgets</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Both Executive and Legislature</t>
+          <t>Execute laws</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Judiciary</t>
+          <t>Make treaties</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Both Executive and Legislature</t>
+          <t>Strike down unconstitutional laws</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>President is head of Executive and Parliament.</t>
+          <t>It safeguards Constitution.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Which principle limits the powers of government organs?</t>
+          <t>Which body checks the actions of the Executive?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Judicial Activism</t>
+          <t>Judiciary</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Separation of Powers</t>
+          <t>Legislature</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Federalism</t>
+          <t>Press</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Universal Adult Franchise</t>
+          <t>Military</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Separation of Powers</t>
+          <t>Judiciary</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Divides power among branches.</t>
+          <t>Judicial review controls Executive excess.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>The power to promulgate ordinances rests with</t>
+          <t>Which organ of the government is responsible for implementing laws?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Legislature</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Speaker of Lok Sabha</t>
+          <t>Judiciary</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Chief Justice</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Under Article 123, President can issue ordinances.</t>
+          <t>The executive enforces the laws.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>In India, the Supreme Court acts as a</t>
+          <t>Which body is responsible for appointing the judges of the High Courts?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Legislature</t>
+          <t>President</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Executive</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Guardian of the Constitution</t>
+          <t>Chief Justice of India and Governor</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Guardian of the Constitution</t>
+          <t>Chief Justice of India and Governor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>It protects constitutional rights.</t>
+          <t>Appointment is made by President after consultation.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>85</v>
+        <v>56</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>The power of the Judiciary to review the Constitutionality of a law is called</t>
+          <t>The President’s power to summon and prorogue Parliament is part of</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Judicial review</t>
+          <t>Executive powers</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Judicial activism</t>
+          <t>Legislative powers</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Judicial restraint</t>
+          <t>Judicial powers</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Judicial supremacy</t>
+          <t>Financial powers</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Judicial review</t>
+          <t>Legislative powers</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>A key feature of Indian judiciary.</t>
+          <t>President as part of Parliament exercises these powers.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>The system where powers overlap but are balanced is called</t>
+          <t>The Legislature can</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Fusion of Powers</t>
+          <t>Make laws</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Separation of Powers</t>
+          <t>Interpret laws</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Partial Fusion</t>
+          <t>Enforce laws</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Checks and Balances</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Checks and Balances</t>
+          <t>Make laws</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Ensures mutual accountability.</t>
+          <t>Its primary function is lawmaking.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>The term ‘checks and balances’ means</t>
+          <t>The Legislature can</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Each organ checks the other’s powers</t>
+          <t>Make laws</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>All powers are in one organ</t>
+          <t>Enforce laws</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Judiciary controls all</t>
+          <t>Interpret laws</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Executive controls Legislature</t>
+          <t>None of the above</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Each organ checks the other’s powers</t>
+          <t>Make laws</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Prevents power abuse.</t>
+          <t>Its primary function is lawmaking.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Which organ has the power to amend the Constitution?</t>
+          <t>In India, which organ controls the budget?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
+          <t>Executive</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Legislature</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
           <t>Judiciary</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Executive</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Parliament</t>
-        </is>
-      </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Press</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Legislature</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Legislature can amend Constitution under Article 368.</t>
+          <t>Parliament controls financial powers.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>The power to issue ordinances lies with</t>
+          <t>Which branch makes laws according to the doctrine of separation of powers?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Judiciary</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Legislature</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Police</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Legislature</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>President can promulgate ordinances.</t>
+          <t>Legislature enacts laws.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Who said “Power tends to corrupt, and absolute power corrupts absolutely”?</t>
+          <t>Who said “Power corrupts; absolute power corrupts absolutely”?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1646,17 +1642,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
+          <t>John Locke</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
           <t>Lord Acton</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>John Locke</t>
-        </is>
-      </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>James Madison</t>
+          <t>Jean-Jacques Rousseau</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1666,709 +1662,705 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Warned about concentration of power.</t>
+          <t>A famous quote on power abuse.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Which branch implements the laws?</t>
+          <t>Which famous case discussed separation of powers and judicial independence?</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Legislature</t>
+          <t>Kesavananda Bharati</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Executive</t>
+          <t>Minerva Mills</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Judiciary</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Press</t>
+          <t>Golaknath</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Executive</t>
+          <t>Minerva Mills</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Responsible for enforcing laws.</t>
+          <t>Emphasized balance between powers.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>The Executive</t>
+          <t>Is there any overlap between powers in Indian system?</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Can veto laws</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Enforces laws</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Interprets laws</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Both a and c</t>
-        </is>
-      </c>
+          <t>Only in emergencies</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Enforces laws</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Executes and administers laws.</t>
+          <t>Overlap exists but balanced by checks.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>57</v>
+        <v>26</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Which of the following is NOT a function of the Executive?</t>
+          <t>Which of the following is NOT a basic feature of the Indian Constitution?</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Implementing laws</t>
+          <t>Separation of Powers</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Making laws</t>
+          <t>Federalism</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Administering policies</t>
+          <t>Judicial Review</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Maintaining public order</t>
+          <t>Absolute Separation of Powers</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Making laws</t>
+          <t>Absolute Separation of Powers</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Lawmaking is primarily Legislature's function.</t>
+          <t>India follows partial separation, not absolute.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Which organ of the government is known as the ‘sword arm’ of the state?</t>
+          <t>The doctrine of separation of powers was first developed by?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Legislature</t>
+          <t>Montesquieu</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Executive</t>
+          <t>John Locke</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Judiciary</t>
+          <t>Thomas Hobbes</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Press</t>
+          <t>Jean-Jacques Rousseau</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Executive</t>
+          <t>Montesquieu</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>The Executive enforces laws and maintains order.</t>
+          <t>He introduced the concept.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>What is the doctrine of Separation of Powers?</t>
+          <t>The doctrine of separation of powers was introduced to</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Division of government powers among Legislature, Executive, Judiciary</t>
+          <t>Avoid concentration of power</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Sharing powers among political parties</t>
+          <t>Ensure efficiency</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Concentration of power in one organ</t>
+          <t>Promote unity</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Division of powers between Centre and State</t>
+          <t>Centralize authority</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Division of government powers among Legislature, Executive, Judiciary</t>
+          <t>Avoid concentration of power</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>It means each branch has distinct functions.</t>
+          <t>Prevents abuse of power.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Who is the head of the Legislature in India?</t>
+          <t>Who said “Power tends to corrupt, and absolute power corrupts absolutely”?</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Montesquieu</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Lord Acton</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Speaker of Lok Sabha</t>
+          <t>John Locke</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Chief Justice</t>
+          <t>James Madison</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Lord Acton</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>He is the head of Parliament.</t>
+          <t>Warned about concentration of power.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Who ensures that the Executive functions according to the law?</t>
+          <t>The principle of separation of powers helps in</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Judiciary</t>
+          <t>Avoiding dictatorship</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Legislature</t>
+          <t>Encouraging dictatorship</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Centralizing power</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Undermining democracy</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Judiciary</t>
+          <t>Avoiding dictatorship</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Through judicial review and writ jurisdiction.</t>
+          <t>Prevents concentration of power.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>In Indian Constitution, which organ has the power to dissolve the Lok Sabha?</t>
+          <t>The Cabinet is part of which organ?</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Legislature</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Chief Justice</t>
+          <t>Judiciary</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>None of the above</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>On advice of Prime Minister.</t>
+          <t>It is the real decision-making body of Executive.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>78</v>
+        <v>98</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Which of the following is a check by the Legislature on the Executive?</t>
+          <t>The President of India acts on the advice of</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Judicial Review</t>
+          <t>Prime Minister and Council of Ministers</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Vote of No-Confidence</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ordinance Power</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Appointment of Judges</t>
+          <t>Speaker of Lok Sabha</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Vote of No-Confidence</t>
+          <t>Prime Minister and Council of Ministers</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Legislature can remove the government by this motion.</t>
+          <t>The real executive authority lies with them.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>73</v>
+        <v>54</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Which organ is responsible for framing the policies of the government?</t>
+          <t>Which constitutional article mandates the separation of judiciary from executive in India?</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Legislature</t>
+          <t>Article 50</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Executive</t>
+          <t>Article 44</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Judiciary</t>
+          <t>Article 37</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Press</t>
+          <t>Article 51</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Executive</t>
+          <t>Article 50</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Executes and formulates policies.</t>
+          <t>Part of DPSP, directs separation for judicial independence.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>70</v>
+        <v>31</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Which of the following best describes the Indian model of separation of powers?</t>
+          <t>Which Article of the Indian Constitution provides for the appointment of the Chief Justice of India?</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Absolute and rigid separation</t>
+          <t>Article 124</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Flexible and overlapping powers</t>
+          <t>Article 217</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Complete fusion</t>
+          <t>Article 50</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>No separation</t>
+          <t>Article 368</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Flexible and overlapping powers</t>
+          <t>Article 124</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Allows cooperation with checks.</t>
+          <t>Provides appointment procedure.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Judiciary independence is protected by</t>
+          <t>Which of the following is a check by the Legislature on the Executive?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Fixed tenure of judges</t>
+          <t>Judicial Review</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Security of tenure</t>
+          <t>Vote of No-Confidence</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Independence of appointment</t>
+          <t>Ordinance Power</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Appointment of Judges</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Vote of No-Confidence</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Ensures impartial judiciary.</t>
+          <t>Legislature can remove the government by this motion.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>The President’s power to summon and prorogue Parliament is part of</t>
+          <t>Which organ enforces the laws in India?</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Executive powers</t>
+          <t>Judiciary</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Legislative powers</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Judicial powers</t>
+          <t>Legislature</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Financial powers</t>
+          <t>None of the above</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Legislative powers</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>President as part of Parliament exercises these powers.</t>
+          <t>The executive implements laws.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>The power of the Executive to reject laws passed by Legislature is called</t>
+          <t>Who is the head of the Legislature in India?</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Judicial Review</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Veto Power</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Ordinance Power</t>
+          <t>Speaker of Lok Sabha</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Amendment Power</t>
+          <t>Chief Justice</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Veto Power</t>
+          <t>President</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>President can veto bills.</t>
+          <t>He is the head of Parliament.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>65</v>
+        <v>97</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Which case established the power of judicial review in India?</t>
+          <t>The principle of Separation of Powers aims at</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Kesavananda Bharati</t>
+          <t>Centralization of power</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Golaknath</t>
+          <t>Distribution of powers</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Marbury v Madison</t>
+          <t>Concentration of power</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Minerva Mills</t>
+          <t>Merger of powers</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Kesavananda Bharati</t>
+          <t>Distribution of powers</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>It upheld the basic structure doctrine.</t>
+          <t>Avoids power concentration.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>18</v>
+        <v>70</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>The Judiciary</t>
+          <t>Which of the following best describes the Indian model of separation of powers?</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Declares laws unconstitutional</t>
+          <t>Absolute and rigid separation</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Enforces laws</t>
+          <t>Flexible and overlapping powers</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Makes laws</t>
+          <t>Complete fusion</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Both a and c</t>
+          <t>No separation</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Declares laws unconstitutional</t>
+          <t>Flexible and overlapping powers</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Protects constitutionality.</t>
+          <t>Allows cooperation with checks.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>7</v>
+        <v>99</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Which article of the Indian Constitution mentions separation of powers explicitly?</t>
+          <t>Which organ appoints the Prime Minister?</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Article 50</t>
+          <t>President</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Article 368</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Article 14</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>No article</t>
+          <t>Chief Justice</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>No article</t>
+          <t>President</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>It is implied, not explicitly mentioned.</t>
+          <t>President appoints PM who commands majority.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>91</v>
+        <v>48</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Which organ controls the government expenditure?</t>
+          <t>Which organ is responsible for enforcing laws?</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
+          <t>Legislature</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
           <t>Executive</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Legislature</t>
-        </is>
-      </c>
       <c r="E49" t="inlineStr">
         <is>
           <t>Judiciary</t>
@@ -2376,187 +2368,187 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Finance Commission</t>
+          <t>Both Legislature and Judiciary</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Legislature</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Parliament controls budget.</t>
+          <t>Executes laws.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>77</v>
+        <v>39</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Who holds the power to dissolve the Lok Sabha?</t>
+          <t>The judiciary in India is independent because</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Judges have security of tenure</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Judges are appointed by Parliament</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Speaker of Lok Sabha</t>
+          <t>Judges can be removed easily</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Chief Justice of India</t>
+          <t>Judges report to Executive</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Judges have security of tenure</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Dissolution is done by the President on PM's advice.</t>
+          <t>Ensures impartial decisions.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Who appoints the Chief Justice of India?</t>
+          <t>The President of India is part of which organ?</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Executive only</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Legislature only</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Both Executive and Legislature</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Supreme Court Judges</t>
+          <t>Judiciary</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Both Executive and Legislature</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>The President appoints CJI.</t>
+          <t>President is head of Executive and Parliament.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Judicial review is an example of</t>
+          <t>Which case established the power of judicial review in India?</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Judiciary checking Legislature</t>
+          <t>Kesavananda Bharati</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Executive controlling Judiciary</t>
+          <t>Golaknath</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Legislature controlling Executive</t>
+          <t>Marbury v Madison</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Legislature checking Judiciary</t>
+          <t>Minerva Mills</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Judiciary checking Legislature</t>
+          <t>Kesavananda Bharati</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Ensures laws are constitutional.</t>
+          <t>It upheld the basic structure doctrine.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Which organ is responsible for enforcing laws?</t>
+          <t>The system where powers overlap but are balanced is called</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Legislature</t>
+          <t>Fusion of Powers</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Executive</t>
+          <t>Separation of Powers</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Judiciary</t>
+          <t>Partial Fusion</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Both Legislature and Judiciary</t>
+          <t>Checks and Balances</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Executive</t>
+          <t>Checks and Balances</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Executes laws.</t>
+          <t>Ensures mutual accountability.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>The Cabinet is part of which organ?</t>
+          <t>In India, the Supreme Court acts as a</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2571,708 +2563,712 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Judiciary</t>
+          <t>Guardian of the Constitution</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>None of the above</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Executive</t>
+          <t>Guardian of the Constitution</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>It is the real decision-making body of Executive.</t>
+          <t>It protects constitutional rights.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>The Indian Constitution follows which kind of separation of powers?</t>
+          <t>The power of the Legislature to check the Executive is exercised through</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Strict Separation</t>
+          <t>No-confidence motion</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Partial Separation</t>
+          <t>Judicial review</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>No Separation</t>
+          <t>Ordinance power</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Complete Merger</t>
+          <t>Amendment power</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Partial Separation</t>
+          <t>No-confidence motion</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Separation with checks and balances.</t>
+          <t>It can remove the government by vote of no-confidence.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>6</v>
+        <v>93</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Which branch interprets the laws?</t>
+          <t>Who is called the ‘Guardian of the Constitution’?</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Legislature</t>
+          <t>President</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Executive</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Judiciary</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Police</t>
+          <t>Attorney General</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Judiciary</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Courts interpret laws.</t>
+          <t>Protects constitutional rights.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>10</v>
+        <v>72</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Which body checks the actions of the Executive?</t>
+          <t>Which principle states that no one should exercise the powers of more than one branch?</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Judiciary</t>
+          <t>Checks and balances</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Legislature</t>
+          <t>Separation of Powers</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Press</t>
+          <t>Federalism</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Military</t>
+          <t>Rule of Law</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Judiciary</t>
+          <t>Separation of Powers</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Judicial review controls Executive excess.</t>
+          <t>Ensures distinct roles.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Which body can impeach a Supreme Court judge?</t>
+          <t>Judges of the Supreme Court can be removed by</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Parliamentary impeachment</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Presidential order</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Chief Justice</t>
+          <t>Executive decision</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Judicial verdict</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Parliamentary impeachment</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Parliament initiates impeachment proceedings.</t>
+          <t>Requires special majority in Parliament.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>The judiciary can</t>
+          <t>The power of judicial review is derived from</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Strike down unconstitutional laws</t>
+          <t>Written Constitution</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Pass budgets</t>
+          <t>Unwritten conventions</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Execute laws</t>
+          <t>Parliamentary resolutions</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Make treaties</t>
+          <t>Presidential orders</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Strike down unconstitutional laws</t>
+          <t>Written Constitution</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>It safeguards Constitution.</t>
+          <t>Explicitly or implicitly provided in the Constitution.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>28</v>
+        <v>75</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Which organ enforces the laws in India?</t>
+          <t>The Constitution of India was adopted in which year?</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Judiciary</t>
+          <t>1947</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Executive</t>
+          <t>1949</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Legislature</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>None of the above</t>
+          <t>1952</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Executive</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>The executive implements laws.</t>
+          <t>Adopted on 26 January 1950.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>54</v>
+        <v>88</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Which constitutional article mandates the separation of judiciary from executive in India?</t>
+          <t>Which of the following is a function of the Legislature?</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Article 50</t>
+          <t>Make laws</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Article 44</t>
+          <t>Implement laws</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Article 37</t>
+          <t>Interpret laws</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Article 51</t>
+          <t>Enforce laws</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Article 50</t>
+          <t>Make laws</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Part of DPSP, directs separation for judicial independence.</t>
+          <t>Lawmaking is the primary role.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>100</v>
+        <v>57</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Which article defines the powers of the Supreme Court?</t>
+          <t>Which of the following is NOT a function of the Executive?</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Article 124</t>
+          <t>Implementing laws</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Article 217</t>
+          <t>Making laws</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Article 50</t>
+          <t>Administering policies</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Article 368</t>
+          <t>Maintaining public order</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Article 124</t>
+          <t>Making laws</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Details appointment and jurisdiction.</t>
+          <t>Lawmaking is primarily Legislature's function.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Which principle states that no one should exercise the powers of more than one branch?</t>
+          <t>Which article defines the powers of the Supreme Court?</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Checks and balances</t>
+          <t>Article 124</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Separation of Powers</t>
+          <t>Article 217</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Federalism</t>
+          <t>Article 50</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rule of Law</t>
+          <t>Article 368</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Separation of Powers</t>
+          <t>Article 124</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Ensures distinct roles.</t>
+          <t>Details appointment and jurisdiction.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>33</v>
+        <v>74</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Judicial review in India is exercised by</t>
+          <t>Who is the constitutional head of the Executive in India?</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Supreme Court only</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>High Courts only</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Both Supreme Court and High Courts</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr"/>
+          <t>Chief Justice</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Both Supreme Court and High Courts</t>
+          <t>President</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Both levels have power of judicial review.</t>
+          <t>Nominal head of the Executive.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>92</v>
+        <v>63</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>The power to promulgate ordinances is vested in</t>
+          <t>Which organ approves the budget?</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Legislature</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Judiciary</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Finance Commission</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Legislature</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Under Article 123.</t>
+          <t>Parliament approves government budget.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>90</v>
+        <v>15</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Which case declared that the basic structure of the Constitution cannot be altered by Parliament?</t>
+          <t>Who suggested the idea of separation of powers in Indian Constitution drafting?</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Kesavananda Bharati</t>
+          <t>B.R. Ambedkar</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Golaknath</t>
+          <t>Mahatma Gandhi</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Minerva Mills</t>
+          <t>Jawaharlal Nehru</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>All of them</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Kesavananda Bharati</t>
+          <t>B.R. Ambedkar</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>The landmark basic structure doctrine case.</t>
+          <t>He explained doctrine in the Constituent Assembly.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Who said “Power corrupts; absolute power corrupts absolutely”?</t>
+          <t>Which organ enforces law and order?</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Montesquieu</t>
+          <t>Judiciary</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>John Locke</t>
+          <t>Legislature</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Lord Acton</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Jean-Jacques Rousseau</t>
+          <t>Press</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lord Acton</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>A famous quote on power abuse.</t>
+          <t>Police and administrative agencies.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>64</v>
+        <v>2</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>The power of judicial review is derived from</t>
+          <t>Who is known as the Father of the Doctrine of Separation of Powers?</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Written Constitution</t>
+          <t>John Locke</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Unwritten conventions</t>
+          <t>Montesquieu</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Parliamentary resolutions</t>
+          <t>Thomas Hobbes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Presidential orders</t>
+          <t>Jean-Jacques Rousseau</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Written Constitution</t>
+          <t>Montesquieu</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Explicitly or implicitly provided in the Constitution.</t>
+          <t>He popularized the concept in “The Spirit of Laws”.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Who is the constitutional head of the Executive in India?</t>
+          <t>Which body can impeach a Supreme Court judge?</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
+          <t>President</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Parliament</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Chief Justice</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
           <t>Prime Minister</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>President</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>Chief Justice</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>Governor</t>
-        </is>
-      </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Nominal head of the Executive.</t>
+          <t>Parliament initiates impeachment proceedings.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Which branch makes laws according to the doctrine of separation of powers?</t>
+          <t>The power to issue ordinances lies with</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Executive</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Judiciary</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Legislature</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Police</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Legislature</t>
+          <t>President</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Legislature enacts laws.</t>
+          <t>President can promulgate ordinances.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>In India, which organ controls the budget?</t>
+          <t>The principle of Separation of Powers helps to</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Executive</t>
+          <t>Prevent misuse of power</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Legislature</t>
+          <t>Concentrate power</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Judiciary</t>
+          <t>Make laws faster</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Press</t>
+          <t>Increase political parties</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Legislature</t>
+          <t>Prevent misuse of power</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Parliament controls financial powers.</t>
+          <t>Avoids arbitrary rule.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>38</v>
+        <v>76</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Which organ interprets the Constitution?</t>
+          <t>Which organ of government in India has the power to grant pardon and reprieve?</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3292,467 +3288,467 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>President</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Judiciary</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Courts interpret laws and Constitution.</t>
+          <t>The President exercises this power as part of the executive.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>The President of India is part of which organs?</t>
+          <t>The power to promulgate ordinances rests with</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Executive only</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Legislature only</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Both Executive and Legislature</t>
+          <t>Speaker of Lok Sabha</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Judiciary</t>
+          <t>Chief Justice</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Both Executive and Legislature</t>
+          <t>President</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>President is constitutional head of both.</t>
+          <t>Under Article 123, President can issue ordinances.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>81</v>
+        <v>43</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Which organ of the government is responsible for implementing laws?</t>
+          <t>The power to impeach the President lies with</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Legislature</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
+          <t>Parliament</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
           <t>Executive</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>Judiciary</t>
-        </is>
-      </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Constitutional Court</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Executive</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>The executive enforces the laws.</t>
+          <t>Parliament initiates impeachment.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>The principle of Separation of Powers helps to</t>
+          <t>Who appoints the Chief Justice of India?</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Prevent misuse of power</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Concentrate power</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Make laws faster</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Increase political parties</t>
+          <t>Supreme Court Judges</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Prevent misuse of power</t>
+          <t>President</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Avoids arbitrary rule.</t>
+          <t>The President appoints CJI.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Judicial review means</t>
+          <t>The independence of judiciary in India is protected by</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Making laws</t>
+          <t>Security of tenure and fixed salaries</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Interpreting laws and declaring laws unconstitutional</t>
+          <t>Appointment by Legislature</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Enforcing laws</t>
+          <t>Removal by Executive</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Approving budget</t>
+          <t>Approval by Parliament</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Interpreting laws and declaring laws unconstitutional</t>
+          <t>Security of tenure and fixed salaries</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Ensures laws comply with Constitution.</t>
+          <t>Ensures impartial judiciary.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>26</v>
+        <v>94</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Which of the following is NOT a basic feature of the Indian Constitution?</t>
+          <t>In India, the power to amend the Constitution lies with</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Separation of Powers</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Federalism</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Judicial Review</t>
+          <t>Judiciary</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Absolute Separation of Powers</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Absolute Separation of Powers</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>India follows partial separation, not absolute.</t>
+          <t>Under Article 368.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Which organ of government appoints judges in India?</t>
+          <t>Separation of powers ensures</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Legislature</t>
+          <t>Concentration of power</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Executive</t>
+          <t>Checks and balances</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Judiciary itself</t>
+          <t>Conflicts among organs</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>President on recommendation</t>
+          <t>Political deadlock</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>President on recommendation</t>
+          <t>Checks and balances</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>President appoints judges on recommendations.</t>
+          <t>Prevents abuse of power.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>The power of the Legislature to check the Executive is exercised through</t>
+          <t>Executive power flows from</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>No-confidence motion</t>
+          <t>Legislature</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Judicial review</t>
+          <t>Judiciary</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Ordinance power</t>
+          <t>President</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Amendment power</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>No-confidence motion</t>
+          <t>President</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>It can remove the government by vote of no-confidence.</t>
+          <t>The President is the nominal executive head.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>The Executive in India is responsible to</t>
+          <t>Which principle limits the powers of government organs?</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>The President</t>
+          <t>Judicial Activism</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>The Judiciary</t>
+          <t>Separation of Powers</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>The Parliament</t>
+          <t>Federalism</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>The Police</t>
+          <t>Universal Adult Franchise</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>The Parliament</t>
+          <t>Separation of Powers</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>It is responsible to the legislature.</t>
+          <t>Divides power among branches.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>The President of India acts on the advice of</t>
+          <t>Which case declared that the basic structure of the Constitution cannot be altered by Parliament?</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Prime Minister and Council of Ministers</t>
+          <t>Kesavananda Bharati</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Golaknath</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Minerva Mills</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Speaker of Lok Sabha</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Prime Minister and Council of Ministers</t>
+          <t>Kesavananda Bharati</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>The real executive authority lies with them.</t>
+          <t>The landmark basic structure doctrine case.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>21</v>
+        <v>85</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>The separation of powers in India is</t>
+          <t>The power of the Judiciary to review the Constitutionality of a law is called</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Strict</t>
+          <t>Judicial review</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Flexible</t>
+          <t>Judicial activism</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Absent</t>
+          <t>Judicial restraint</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Unconstitutional</t>
+          <t>Judicial supremacy</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Flexible</t>
+          <t>Judicial review</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Allows cooperation among branches.</t>
+          <t>A key feature of Indian judiciary.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Which Article of the Indian Constitution provides for the appointment of the Chief Justice of India?</t>
+          <t>Which branch interprets the laws?</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Article 124</t>
+          <t>Legislature</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Article 217</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Article 50</t>
+          <t>Judiciary</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Article 368</t>
+          <t>Police</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Article 124</t>
+          <t>Judiciary</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Provides appointment procedure.</t>
+          <t>Courts interpret laws.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>95</v>
+        <v>30</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>The executive is responsible to</t>
+          <t>Which organ of government appoints judges in India?</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3762,703 +3758,707 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Judiciary</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Judiciary itself</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Election Commission</t>
+          <t>President on recommendation</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Legislature</t>
+          <t>President on recommendation</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Executive is accountable to Parliament.</t>
+          <t>President appoints judges on recommendations.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>27</v>
+        <v>82</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Which organ has the power to make laws in India?</t>
+          <t>Judicial review means</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Judiciary</t>
+          <t>Making laws</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Executive</t>
+          <t>Interpreting laws and declaring laws unconstitutional</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Legislature</t>
+          <t>Enforcing laws</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Approving budget</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Legislature</t>
+          <t>Interpreting laws and declaring laws unconstitutional</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Legislature makes laws.</t>
+          <t>Ensures laws comply with Constitution.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>34</v>
+        <v>83</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Which of the following cases emphasized the importance of separation of powers?</t>
+          <t>The President of India is part of which organs?</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Kesavananda Bharati</t>
+          <t>Executive only</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Minerva Mills</t>
+          <t>Legislature only</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Golak Nath</t>
+          <t>Both Executive and Legislature</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Indira Gandhi Case</t>
+          <t>Judiciary</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Kesavananda Bharati</t>
+          <t>Both Executive and Legislature</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Upheld basic structure doctrine including separation of powers.</t>
+          <t>President is constitutional head of both.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>36</v>
+        <v>95</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Who holds the real executive power in India?</t>
+          <t>The executive is responsible to</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
+          <t>Legislature</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Judiciary</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
           <t>President</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>Prime Minister and Council of Ministers</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>Parliament</t>
-        </is>
-      </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Election Commission</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Prime Minister and Council of Ministers</t>
+          <t>Legislature</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>They hold actual power.</t>
+          <t>Executive is accountable to Parliament.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>In India, the power to amend the Constitution lies with</t>
+          <t>The executive in India is</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Constitutional and political</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Absolute</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Judiciary</t>
+          <t>Legislative</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Judicial</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Constitutional and political</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Under Article 368.</t>
+          <t>It functions within constitutional limits.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Who suggested the idea of separation of powers in Indian Constitution drafting?</t>
+          <t>Which of the following cases emphasized the importance of separation of powers?</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>B.R. Ambedkar</t>
+          <t>Kesavananda Bharati</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Mahatma Gandhi</t>
+          <t>Minerva Mills</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Jawaharlal Nehru</t>
+          <t>Golak Nath</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>All of them</t>
+          <t>Indira Gandhi Case</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>B.R. Ambedkar</t>
+          <t>Kesavananda Bharati</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>He explained doctrine in the Constituent Assembly.</t>
+          <t>Upheld basic structure doctrine including separation of powers.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>13</v>
+        <v>58</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Which is a feature of partial separation of powers in India?</t>
+          <t>Judicial independence in India is protected by</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Judges can be executive officers</t>
+          <t>Security of tenure</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Legislature controls Judiciary</t>
+          <t>Fixed salary</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Executive is responsible to Legislature</t>
+          <t>Prohibition of arbitrary removal</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>No checks and balances</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Executive is responsible to Legislature</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Shows overlap but with accountability.</t>
+          <t>Ensures impartiality and fairness.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>97</v>
+        <v>36</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>The principle of Separation of Powers aims at</t>
+          <t>Who holds the real executive power in India?</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Centralization of power</t>
+          <t>President</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Distribution of powers</t>
+          <t>Prime Minister and Council of Ministers</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Concentration of power</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Merger of powers</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Distribution of powers</t>
+          <t>Prime Minister and Council of Ministers</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Avoids power concentration.</t>
+          <t>They hold actual power.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>76</v>
+        <v>7</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Which organ of government in India has the power to grant pardon and reprieve?</t>
+          <t>Which article of the Indian Constitution mentions separation of powers explicitly?</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Legislature</t>
+          <t>Article 50</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Executive</t>
+          <t>Article 368</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Judiciary</t>
+          <t>Article 14</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>No article</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Executive</t>
+          <t>No article</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>The President exercises this power as part of the executive.</t>
+          <t>It is implied, not explicitly mentioned.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>79</v>
+        <v>29</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Which body is responsible for appointing the judges of the High Courts?</t>
+          <t>The Indian Constitution follows which kind of separation of powers?</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Strict Separation</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Partial Separation</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Chief Justice of India and Governor</t>
+          <t>No Separation</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Complete Merger</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Chief Justice of India and Governor</t>
+          <t>Partial Separation</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Appointment is made by President after consultation.</t>
+          <t>Separation with checks and balances.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>88</v>
+        <v>17</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Which of the following is a function of the Legislature?</t>
+          <t>The Executive</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Make laws</t>
+          <t>Can veto laws</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Implement laws</t>
+          <t>Enforces laws</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Interpret laws</t>
+          <t>Interprets laws</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Enforce laws</t>
+          <t>Both a and c</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Make laws</t>
+          <t>Enforces laws</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Lawmaking is the primary role.</t>
+          <t>Executes and administers laws.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Which organ enforces law and order?</t>
+          <t>Which organ is responsible for framing the policies of the government?</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
+          <t>Legislature</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Executive</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
           <t>Judiciary</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>Legislature</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Press</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
         <is>
           <t>Executive</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>Press</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>Executive</t>
-        </is>
-      </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Police and administrative agencies.</t>
+          <t>Executes and formulates policies.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>32</v>
+        <v>92</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>The doctrine of separation of powers was first developed by?</t>
+          <t>The power to promulgate ordinances is vested in</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Montesquieu</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>John Locke</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Thomas Hobbes</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Jean-Jacques Rousseau</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Montesquieu</t>
+          <t>President</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>He introduced the concept.</t>
+          <t>Under Article 123.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>71</v>
+        <v>35</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Judges of the Supreme Court can be removed by</t>
+          <t>The power of the Executive to reject laws passed by Legislature is called</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Parliamentary impeachment</t>
+          <t>Judicial Review</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Presidential order</t>
+          <t>Veto Power</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Executive decision</t>
+          <t>Ordinance Power</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Judicial verdict</t>
+          <t>Amendment Power</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Parliamentary impeachment</t>
+          <t>Veto Power</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Requires special majority in Parliament.</t>
+          <t>President can veto bills.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>The Legislature can</t>
+          <t>Separation of powers helps in</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Make laws</t>
+          <t>Consolidating power</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Enforce laws</t>
+          <t>Democracy and accountability</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Interpret laws</t>
+          <t>Dictatorship</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>None of the above</t>
+          <t>Political stability only</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Make laws</t>
+          <t>Democracy and accountability</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Its primary function is lawmaking.</t>
+          <t>Ensures balanced governance.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Which famous case discussed separation of powers and judicial independence?</t>
+          <t>Which organ interprets the Constitution?</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Kesavananda Bharati</t>
+          <t>Legislature</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Minerva Mills</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Judiciary</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Golaknath</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Minerva Mills</t>
+          <t>Judiciary</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Emphasized balance between powers.</t>
+          <t>Courts interpret laws and Constitution.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>The principle of separation of powers helps in</t>
+          <t>The Indian Constitution provides for</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Avoiding dictatorship</t>
+          <t>Absolute separation of powers</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Encouraging dictatorship</t>
+          <t>Partial separation with checks</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Centralizing power</t>
+          <t>No separation of powers</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Undermining democracy</t>
+          <t>Fusion of powers</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Avoiding dictatorship</t>
+          <t>Partial separation with checks</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Prevents concentration of power.</t>
+          <t>Balances power among organs.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Is there any overlap between powers in Indian system?</t>
+          <t>The Executive in India is responsible to</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>The President</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>The Judiciary</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Only in emergencies</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr"/>
+          <t>The Parliament</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>The Police</t>
+        </is>
+      </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>The Parliament</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Overlap exists but balanced by checks.</t>
+          <t>It is responsible to the legislature.</t>
         </is>
       </c>
     </row>
